--- a/data/crudo/Test_inicial.xlsx
+++ b/data/crudo/Test_inicial.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q390"/>
+  <dimension ref="A1:Q465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25794,6 +25794,4881 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Bastian Valentino</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Huanio Marreros</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>13</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>1</v>
+      </c>
+      <c r="H391" t="n">
+        <v>1</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>1</v>
+      </c>
+      <c r="K391" t="n">
+        <v>1</v>
+      </c>
+      <c r="L391" t="n">
+        <v>0</v>
+      </c>
+      <c r="M391" t="n">
+        <v>1</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Eduardo Lionel</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Guerrero Muñoz</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>13</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>1</v>
+      </c>
+      <c r="H392" t="n">
+        <v>2</v>
+      </c>
+      <c r="I392" t="n">
+        <v>2</v>
+      </c>
+      <c r="J392" t="n">
+        <v>3</v>
+      </c>
+      <c r="K392" t="n">
+        <v>1</v>
+      </c>
+      <c r="L392" t="n">
+        <v>1</v>
+      </c>
+      <c r="M392" t="n">
+        <v>0</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" t="n">
+        <v>1</v>
+      </c>
+      <c r="P392" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valentina mayteé </t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>alayo mera</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>1 b</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>13</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>3</v>
+      </c>
+      <c r="H393" t="n">
+        <v>1</v>
+      </c>
+      <c r="I393" t="n">
+        <v>2</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1</v>
+      </c>
+      <c r="K393" t="n">
+        <v>1</v>
+      </c>
+      <c r="L393" t="n">
+        <v>3</v>
+      </c>
+      <c r="M393" t="n">
+        <v>1</v>
+      </c>
+      <c r="N393" t="n">
+        <v>1</v>
+      </c>
+      <c r="O393" t="n">
+        <v>3</v>
+      </c>
+      <c r="P393" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Itana Marlith</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Olaya Montoya</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>13</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>1</v>
+      </c>
+      <c r="H394" t="n">
+        <v>1</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>2</v>
+      </c>
+      <c r="K394" t="n">
+        <v>1</v>
+      </c>
+      <c r="L394" t="n">
+        <v>1</v>
+      </c>
+      <c r="M394" t="n">
+        <v>1</v>
+      </c>
+      <c r="N394" t="n">
+        <v>1</v>
+      </c>
+      <c r="O394" t="n">
+        <v>1</v>
+      </c>
+      <c r="P394" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Joaquin Mathias</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Leiva Raymundes</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>1°</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>13</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>1</v>
+      </c>
+      <c r="H395" t="n">
+        <v>1</v>
+      </c>
+      <c r="I395" t="n">
+        <v>1</v>
+      </c>
+      <c r="J395" t="n">
+        <v>1</v>
+      </c>
+      <c r="K395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" t="n">
+        <v>1</v>
+      </c>
+      <c r="M395" t="n">
+        <v>2</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>1</v>
+      </c>
+      <c r="P395" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Luana Alexa</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Fiestas</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>13</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>2</v>
+      </c>
+      <c r="H396" t="n">
+        <v>2</v>
+      </c>
+      <c r="I396" t="n">
+        <v>3</v>
+      </c>
+      <c r="J396" t="n">
+        <v>2</v>
+      </c>
+      <c r="K396" t="n">
+        <v>1</v>
+      </c>
+      <c r="L396" t="n">
+        <v>3</v>
+      </c>
+      <c r="M396" t="n">
+        <v>1</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>1</v>
+      </c>
+      <c r="P396" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Mego Rodriguez</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>13</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>0</v>
+      </c>
+      <c r="L397" t="n">
+        <v>0</v>
+      </c>
+      <c r="M397" t="n">
+        <v>1</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="P397" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Minimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>12</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>0</v>
+      </c>
+      <c r="K398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0</v>
+      </c>
+      <c r="M398" t="n">
+        <v>0</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Minimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ashley</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>campos</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>1ro B secu</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>12</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>3</v>
+      </c>
+      <c r="H399" t="n">
+        <v>1</v>
+      </c>
+      <c r="I399" t="n">
+        <v>3</v>
+      </c>
+      <c r="J399" t="n">
+        <v>2</v>
+      </c>
+      <c r="K399" t="n">
+        <v>3</v>
+      </c>
+      <c r="L399" t="n">
+        <v>3</v>
+      </c>
+      <c r="M399" t="n">
+        <v>3</v>
+      </c>
+      <c r="N399" t="n">
+        <v>1</v>
+      </c>
+      <c r="O399" t="n">
+        <v>2</v>
+      </c>
+      <c r="P399" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Luis Santiago</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Maurtua Diaz</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>1°</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>13</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>1</v>
+      </c>
+      <c r="H400" t="n">
+        <v>1</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1</v>
+      </c>
+      <c r="J400" t="n">
+        <v>2</v>
+      </c>
+      <c r="K400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" t="n">
+        <v>0</v>
+      </c>
+      <c r="M400" t="n">
+        <v>1</v>
+      </c>
+      <c r="N400" t="n">
+        <v>1</v>
+      </c>
+      <c r="O400" t="n">
+        <v>1</v>
+      </c>
+      <c r="P400" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Matew Abel</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Dueñas Villalobos</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>13</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>1</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3</v>
+      </c>
+      <c r="I401" t="n">
+        <v>2</v>
+      </c>
+      <c r="J401" t="n">
+        <v>1</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" t="n">
+        <v>1</v>
+      </c>
+      <c r="M401" t="n">
+        <v>1</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+      <c r="P401" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leandro </t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peña </t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>1 b</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>12</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>1</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2</v>
+      </c>
+      <c r="I402" t="n">
+        <v>3</v>
+      </c>
+      <c r="J402" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" t="n">
+        <v>1</v>
+      </c>
+      <c r="L402" t="n">
+        <v>2</v>
+      </c>
+      <c r="M402" t="n">
+        <v>0</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
+      <c r="P402" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mia fernanda </t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sánchez </t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>1ro</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>13</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>3</v>
+      </c>
+      <c r="H403" t="n">
+        <v>2</v>
+      </c>
+      <c r="I403" t="n">
+        <v>1</v>
+      </c>
+      <c r="J403" t="n">
+        <v>1</v>
+      </c>
+      <c r="K403" t="n">
+        <v>2</v>
+      </c>
+      <c r="L403" t="n">
+        <v>3</v>
+      </c>
+      <c r="M403" t="n">
+        <v>3</v>
+      </c>
+      <c r="N403" t="n">
+        <v>1</v>
+      </c>
+      <c r="O403" t="n">
+        <v>3</v>
+      </c>
+      <c r="P403" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Akemi Gianna</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Pauccar Caycho</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>13</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>2</v>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
+      </c>
+      <c r="I404" t="n">
+        <v>3</v>
+      </c>
+      <c r="J404" t="n">
+        <v>2</v>
+      </c>
+      <c r="K404" t="n">
+        <v>1</v>
+      </c>
+      <c r="L404" t="n">
+        <v>1</v>
+      </c>
+      <c r="M404" t="n">
+        <v>0</v>
+      </c>
+      <c r="N404" t="n">
+        <v>1</v>
+      </c>
+      <c r="O404" t="n">
+        <v>1</v>
+      </c>
+      <c r="P404" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>FABIANO</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>GÓMES</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>1RO SECUNDARIA?</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>12</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>1</v>
+      </c>
+      <c r="H405" t="n">
+        <v>2</v>
+      </c>
+      <c r="I405" t="n">
+        <v>3</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="n">
+        <v>1</v>
+      </c>
+      <c r="M405" t="n">
+        <v>1</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
+      <c r="P405" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Castillo</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>12</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>1</v>
+      </c>
+      <c r="H406" t="n">
+        <v>1</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0</v>
+      </c>
+      <c r="L406" t="n">
+        <v>0</v>
+      </c>
+      <c r="M406" t="n">
+        <v>2</v>
+      </c>
+      <c r="N406" t="n">
+        <v>1</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+      <c r="P406" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Poma</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>1°</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>12</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="n">
+        <v>1</v>
+      </c>
+      <c r="I407" t="n">
+        <v>2</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" t="n">
+        <v>1</v>
+      </c>
+      <c r="L407" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" t="n">
+        <v>1</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
+        <v>3</v>
+      </c>
+      <c r="P407" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Xiomara Thais A</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Almendras Alarcon</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>1 b</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>13</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>3</v>
+      </c>
+      <c r="H408" t="n">
+        <v>1</v>
+      </c>
+      <c r="I408" t="n">
+        <v>1</v>
+      </c>
+      <c r="J408" t="n">
+        <v>2</v>
+      </c>
+      <c r="K408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L408" t="n">
+        <v>1</v>
+      </c>
+      <c r="M408" t="n">
+        <v>1</v>
+      </c>
+      <c r="N408" t="n">
+        <v>1</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Ivanna Shecik  A</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Echegaray Robles</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>1"B"</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>12</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" t="n">
+        <v>2</v>
+      </c>
+      <c r="I409" t="n">
+        <v>3</v>
+      </c>
+      <c r="J409" t="n">
+        <v>3</v>
+      </c>
+      <c r="K409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L409" t="n">
+        <v>1</v>
+      </c>
+      <c r="M409" t="n">
+        <v>3</v>
+      </c>
+      <c r="N409" t="n">
+        <v>1</v>
+      </c>
+      <c r="O409" t="n">
+        <v>1</v>
+      </c>
+      <c r="P409" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>antonella gya</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>pachas romero</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>13</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>3</v>
+      </c>
+      <c r="H410" t="n">
+        <v>1</v>
+      </c>
+      <c r="I410" t="n">
+        <v>3</v>
+      </c>
+      <c r="J410" t="n">
+        <v>3</v>
+      </c>
+      <c r="K410" t="n">
+        <v>3</v>
+      </c>
+      <c r="L410" t="n">
+        <v>3</v>
+      </c>
+      <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>3</v>
+      </c>
+      <c r="P410" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aysel </t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aliaga amaringo </t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>1 b</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>13</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>3</v>
+      </c>
+      <c r="H411" t="n">
+        <v>2</v>
+      </c>
+      <c r="I411" t="n">
+        <v>1</v>
+      </c>
+      <c r="J411" t="n">
+        <v>3</v>
+      </c>
+      <c r="K411" t="n">
+        <v>3</v>
+      </c>
+      <c r="L411" t="n">
+        <v>3</v>
+      </c>
+      <c r="M411" t="n">
+        <v>3</v>
+      </c>
+      <c r="N411" t="n">
+        <v>1</v>
+      </c>
+      <c r="O411" t="n">
+        <v>3</v>
+      </c>
+      <c r="P411" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francesca valentina </t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Jaen delgadillo</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>1ro</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>12</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>1</v>
+      </c>
+      <c r="H412" t="n">
+        <v>1</v>
+      </c>
+      <c r="I412" t="n">
+        <v>2</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1</v>
+      </c>
+      <c r="K412" t="n">
+        <v>2</v>
+      </c>
+      <c r="L412" t="n">
+        <v>2</v>
+      </c>
+      <c r="M412" t="n">
+        <v>1</v>
+      </c>
+      <c r="N412" t="n">
+        <v>2</v>
+      </c>
+      <c r="O412" t="n">
+        <v>2</v>
+      </c>
+      <c r="P412" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>gya hanady</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donayre roman </t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>1ro</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>13</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>1</v>
+      </c>
+      <c r="H413" t="n">
+        <v>3</v>
+      </c>
+      <c r="I413" t="n">
+        <v>1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>2</v>
+      </c>
+      <c r="K413" t="n">
+        <v>1</v>
+      </c>
+      <c r="L413" t="n">
+        <v>1</v>
+      </c>
+      <c r="M413" t="n">
+        <v>2</v>
+      </c>
+      <c r="N413" t="n">
+        <v>1</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Salvador Leandro</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Cuito</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>13</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" t="n">
+        <v>1</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" t="n">
+        <v>0</v>
+      </c>
+      <c r="M414" t="n">
+        <v>0</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Minimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Eduardo Nicolas a</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>LAVÁN</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>12</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>1</v>
+      </c>
+      <c r="H415" t="n">
+        <v>1</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" t="n">
+        <v>1</v>
+      </c>
+      <c r="M415" t="n">
+        <v>0</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0</v>
+      </c>
+      <c r="P415" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Minimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Thiago Ricardo</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Cabrera Bedón</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>1re Año "B"</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>13</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>1</v>
+      </c>
+      <c r="H416" t="n">
+        <v>1</v>
+      </c>
+      <c r="I416" t="n">
+        <v>2</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1</v>
+      </c>
+      <c r="K416" t="n">
+        <v>1</v>
+      </c>
+      <c r="L416" t="n">
+        <v>3</v>
+      </c>
+      <c r="M416" t="n">
+        <v>3</v>
+      </c>
+      <c r="N416" t="n">
+        <v>1</v>
+      </c>
+      <c r="O416" t="n">
+        <v>1</v>
+      </c>
+      <c r="P416" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Dharling ELENA A</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>DIAZ CARREÑO</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>13</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>3</v>
+      </c>
+      <c r="H417" t="n">
+        <v>2</v>
+      </c>
+      <c r="I417" t="n">
+        <v>3</v>
+      </c>
+      <c r="J417" t="n">
+        <v>3</v>
+      </c>
+      <c r="K417" t="n">
+        <v>3</v>
+      </c>
+      <c r="L417" t="n">
+        <v>3</v>
+      </c>
+      <c r="M417" t="n">
+        <v>3</v>
+      </c>
+      <c r="N417" t="n">
+        <v>3</v>
+      </c>
+      <c r="O417" t="n">
+        <v>3</v>
+      </c>
+      <c r="P417" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Fabiana Melissa m</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Caceres Leon</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>1 B secundaria</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>12</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>2</v>
+      </c>
+      <c r="H418" t="n">
+        <v>2</v>
+      </c>
+      <c r="I418" t="n">
+        <v>2</v>
+      </c>
+      <c r="J418" t="n">
+        <v>2</v>
+      </c>
+      <c r="K418" t="n">
+        <v>2</v>
+      </c>
+      <c r="L418" t="n">
+        <v>2</v>
+      </c>
+      <c r="M418" t="n">
+        <v>2</v>
+      </c>
+      <c r="N418" t="n">
+        <v>2</v>
+      </c>
+      <c r="O418" t="n">
+        <v>1</v>
+      </c>
+      <c r="P418" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>alisson camila</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>herencia</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>1ro B</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>13</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0</v>
+      </c>
+      <c r="I419" t="n">
+        <v>3</v>
+      </c>
+      <c r="J419" t="n">
+        <v>3</v>
+      </c>
+      <c r="K419" t="n">
+        <v>3</v>
+      </c>
+      <c r="L419" t="n">
+        <v>3</v>
+      </c>
+      <c r="M419" t="n">
+        <v>3</v>
+      </c>
+      <c r="N419" t="n">
+        <v>3</v>
+      </c>
+      <c r="O419" t="n">
+        <v>3</v>
+      </c>
+      <c r="P419" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Micaewa Sofía </t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Rojas Zegarra</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>1 "B"</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>12</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>3</v>
+      </c>
+      <c r="H420" t="n">
+        <v>3</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="n">
+        <v>1</v>
+      </c>
+      <c r="K420" t="n">
+        <v>3</v>
+      </c>
+      <c r="L420" t="n">
+        <v>3</v>
+      </c>
+      <c r="M420" t="n">
+        <v>2</v>
+      </c>
+      <c r="N420" t="n">
+        <v>3</v>
+      </c>
+      <c r="O420" t="n">
+        <v>3</v>
+      </c>
+      <c r="P420" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Kamila Elena</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Obregon</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>13</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>3</v>
+      </c>
+      <c r="H421" t="n">
+        <v>3</v>
+      </c>
+      <c r="I421" t="n">
+        <v>3</v>
+      </c>
+      <c r="J421" t="n">
+        <v>3</v>
+      </c>
+      <c r="K421" t="n">
+        <v>2</v>
+      </c>
+      <c r="L421" t="n">
+        <v>3</v>
+      </c>
+      <c r="M421" t="n">
+        <v>2</v>
+      </c>
+      <c r="N421" t="n">
+        <v>3</v>
+      </c>
+      <c r="O421" t="n">
+        <v>3</v>
+      </c>
+      <c r="P421" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lionel </t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Rondon</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>16</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>1</v>
+      </c>
+      <c r="H422" t="n">
+        <v>1</v>
+      </c>
+      <c r="I422" t="n">
+        <v>1</v>
+      </c>
+      <c r="J422" t="n">
+        <v>1</v>
+      </c>
+      <c r="K422" t="n">
+        <v>1</v>
+      </c>
+      <c r="L422" t="n">
+        <v>0</v>
+      </c>
+      <c r="M422" t="n">
+        <v>0</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+      <c r="P422" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>walewska fabiana</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>ormeño molina</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>5to C</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>16</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>3</v>
+      </c>
+      <c r="H423" t="n">
+        <v>3</v>
+      </c>
+      <c r="I423" t="n">
+        <v>2</v>
+      </c>
+      <c r="J423" t="n">
+        <v>3</v>
+      </c>
+      <c r="K423" t="n">
+        <v>3</v>
+      </c>
+      <c r="L423" t="n">
+        <v>2</v>
+      </c>
+      <c r="M423" t="n">
+        <v>2</v>
+      </c>
+      <c r="N423" t="n">
+        <v>2</v>
+      </c>
+      <c r="O423" t="n">
+        <v>2</v>
+      </c>
+      <c r="P423" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Bruss</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Palomino</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>5 secundaria</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>17</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>1</v>
+      </c>
+      <c r="H424" t="n">
+        <v>1</v>
+      </c>
+      <c r="I424" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" t="n">
+        <v>3</v>
+      </c>
+      <c r="K424" t="n">
+        <v>1</v>
+      </c>
+      <c r="L424" t="n">
+        <v>3</v>
+      </c>
+      <c r="M424" t="n">
+        <v>2</v>
+      </c>
+      <c r="N424" t="n">
+        <v>2</v>
+      </c>
+      <c r="O424" t="n">
+        <v>1</v>
+      </c>
+      <c r="P424" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Graciela Ines</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Fernandez Barrios</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>5toc</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>17</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>1</v>
+      </c>
+      <c r="H425" t="n">
+        <v>2</v>
+      </c>
+      <c r="I425" t="n">
+        <v>2</v>
+      </c>
+      <c r="J425" t="n">
+        <v>3</v>
+      </c>
+      <c r="K425" t="n">
+        <v>2</v>
+      </c>
+      <c r="L425" t="n">
+        <v>2</v>
+      </c>
+      <c r="M425" t="n">
+        <v>1</v>
+      </c>
+      <c r="N425" t="n">
+        <v>1</v>
+      </c>
+      <c r="O425" t="n">
+        <v>1</v>
+      </c>
+      <c r="P425" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayron jose </t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">castro </t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>17</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>1</v>
+      </c>
+      <c r="H426" t="n">
+        <v>1</v>
+      </c>
+      <c r="I426" t="n">
+        <v>1</v>
+      </c>
+      <c r="J426" t="n">
+        <v>1</v>
+      </c>
+      <c r="K426" t="n">
+        <v>1</v>
+      </c>
+      <c r="L426" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" t="n">
+        <v>0</v>
+      </c>
+      <c r="N426" t="n">
+        <v>3</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
+      <c r="P426" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Tello</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>5 C</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>16</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>3</v>
+      </c>
+      <c r="H427" t="n">
+        <v>2</v>
+      </c>
+      <c r="I427" t="n">
+        <v>1</v>
+      </c>
+      <c r="J427" t="n">
+        <v>2</v>
+      </c>
+      <c r="K427" t="n">
+        <v>2</v>
+      </c>
+      <c r="L427" t="n">
+        <v>2</v>
+      </c>
+      <c r="M427" t="n">
+        <v>1</v>
+      </c>
+      <c r="N427" t="n">
+        <v>1</v>
+      </c>
+      <c r="O427" t="n">
+        <v>2</v>
+      </c>
+      <c r="P427" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Juleisy</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>17</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>2</v>
+      </c>
+      <c r="H428" t="n">
+        <v>1</v>
+      </c>
+      <c r="I428" t="n">
+        <v>3</v>
+      </c>
+      <c r="J428" t="n">
+        <v>1</v>
+      </c>
+      <c r="K428" t="n">
+        <v>3</v>
+      </c>
+      <c r="L428" t="n">
+        <v>1</v>
+      </c>
+      <c r="M428" t="n">
+        <v>1</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>1</v>
+      </c>
+      <c r="P428" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Thiago Javier</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Alcalde</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>5to C</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>17</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>1</v>
+      </c>
+      <c r="H429" t="n">
+        <v>1</v>
+      </c>
+      <c r="I429" t="n">
+        <v>2</v>
+      </c>
+      <c r="J429" t="n">
+        <v>1</v>
+      </c>
+      <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="n">
+        <v>1</v>
+      </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" t="n">
+        <v>1</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="P429" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abel Akira </t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martinez Mori </t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>16</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>1</v>
+      </c>
+      <c r="H430" t="n">
+        <v>2</v>
+      </c>
+      <c r="I430" t="n">
+        <v>3</v>
+      </c>
+      <c r="J430" t="n">
+        <v>1</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="n">
+        <v>2</v>
+      </c>
+      <c r="M430" t="n">
+        <v>1</v>
+      </c>
+      <c r="N430" t="n">
+        <v>1</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="P430" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Xiang M</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Wong Elespuru</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>5 c</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>17</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>3</v>
+      </c>
+      <c r="H431" t="n">
+        <v>2</v>
+      </c>
+      <c r="I431" t="n">
+        <v>3</v>
+      </c>
+      <c r="J431" t="n">
+        <v>3</v>
+      </c>
+      <c r="K431" t="n">
+        <v>3</v>
+      </c>
+      <c r="L431" t="n">
+        <v>3</v>
+      </c>
+      <c r="M431" t="n">
+        <v>3</v>
+      </c>
+      <c r="N431" t="n">
+        <v>3</v>
+      </c>
+      <c r="O431" t="n">
+        <v>3</v>
+      </c>
+      <c r="P431" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Andrea antonella a</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Perez</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>17</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>3</v>
+      </c>
+      <c r="H432" t="n">
+        <v>1</v>
+      </c>
+      <c r="I432" t="n">
+        <v>1</v>
+      </c>
+      <c r="J432" t="n">
+        <v>1</v>
+      </c>
+      <c r="K432" t="n">
+        <v>3</v>
+      </c>
+      <c r="L432" t="n">
+        <v>3</v>
+      </c>
+      <c r="M432" t="n">
+        <v>3</v>
+      </c>
+      <c r="N432" t="n">
+        <v>3</v>
+      </c>
+      <c r="O432" t="n">
+        <v>2</v>
+      </c>
+      <c r="P432" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Alarcon</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>5 B Secundaria</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>17</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>1</v>
+      </c>
+      <c r="H433" t="n">
+        <v>1</v>
+      </c>
+      <c r="I433" t="n">
+        <v>2</v>
+      </c>
+      <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" t="n">
+        <v>1</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Daniela gisselle</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Alzamora</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>17</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>2</v>
+      </c>
+      <c r="H434" t="n">
+        <v>2</v>
+      </c>
+      <c r="I434" t="n">
+        <v>3</v>
+      </c>
+      <c r="J434" t="n">
+        <v>3</v>
+      </c>
+      <c r="K434" t="n">
+        <v>3</v>
+      </c>
+      <c r="L434" t="n">
+        <v>1</v>
+      </c>
+      <c r="M434" t="n">
+        <v>3</v>
+      </c>
+      <c r="N434" t="n">
+        <v>2</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>fatima nicole</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>paredes arroyo</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>5toc</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>17</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>1</v>
+      </c>
+      <c r="H435" t="n">
+        <v>1</v>
+      </c>
+      <c r="I435" t="n">
+        <v>2</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2</v>
+      </c>
+      <c r="K435" t="n">
+        <v>1</v>
+      </c>
+      <c r="L435" t="n">
+        <v>1</v>
+      </c>
+      <c r="M435" t="n">
+        <v>2</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>1</v>
+      </c>
+      <c r="P435" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>stefany valentina</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>mora</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>5c</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>17</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>1</v>
+      </c>
+      <c r="H436" t="n">
+        <v>1</v>
+      </c>
+      <c r="I436" t="n">
+        <v>2</v>
+      </c>
+      <c r="J436" t="n">
+        <v>1</v>
+      </c>
+      <c r="K436" t="n">
+        <v>1</v>
+      </c>
+      <c r="L436" t="n">
+        <v>1</v>
+      </c>
+      <c r="M436" t="n">
+        <v>1</v>
+      </c>
+      <c r="N436" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="P436" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>César Orlando  A</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Gutiérrez Duque</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>16</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>1</v>
+      </c>
+      <c r="H437" t="n">
+        <v>2</v>
+      </c>
+      <c r="I437" t="n">
+        <v>1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>3</v>
+      </c>
+      <c r="K437" t="n">
+        <v>2</v>
+      </c>
+      <c r="L437" t="n">
+        <v>1</v>
+      </c>
+      <c r="M437" t="n">
+        <v>2</v>
+      </c>
+      <c r="N437" t="n">
+        <v>1</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Shanon</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Evangelista</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>5 secundaria</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>16</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>3</v>
+      </c>
+      <c r="H438" t="n">
+        <v>3</v>
+      </c>
+      <c r="I438" t="n">
+        <v>3</v>
+      </c>
+      <c r="J438" t="n">
+        <v>3</v>
+      </c>
+      <c r="K438" t="n">
+        <v>2</v>
+      </c>
+      <c r="L438" t="n">
+        <v>3</v>
+      </c>
+      <c r="M438" t="n">
+        <v>3</v>
+      </c>
+      <c r="N438" t="n">
+        <v>2</v>
+      </c>
+      <c r="O438" t="n">
+        <v>1</v>
+      </c>
+      <c r="P438" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Sebastian LL</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sayan Plasencia </t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>5to Año C</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>17</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>1</v>
+      </c>
+      <c r="H439" t="n">
+        <v>1</v>
+      </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" t="n">
+        <v>1</v>
+      </c>
+      <c r="K439" t="n">
+        <v>1</v>
+      </c>
+      <c r="L439" t="n">
+        <v>1</v>
+      </c>
+      <c r="M439" t="n">
+        <v>2</v>
+      </c>
+      <c r="N439" t="n">
+        <v>2</v>
+      </c>
+      <c r="O439" t="n">
+        <v>1</v>
+      </c>
+      <c r="P439" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Oscar Alonso</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Ocupa Chapoñan</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>17</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>2</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1</v>
+      </c>
+      <c r="I440" t="n">
+        <v>3</v>
+      </c>
+      <c r="J440" t="n">
+        <v>2</v>
+      </c>
+      <c r="K440" t="n">
+        <v>2</v>
+      </c>
+      <c r="L440" t="n">
+        <v>1</v>
+      </c>
+      <c r="M440" t="n">
+        <v>2</v>
+      </c>
+      <c r="N440" t="n">
+        <v>3</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Jamile Ariana Mar</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Morales Arce</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>17</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>1</v>
+      </c>
+      <c r="H441" t="n">
+        <v>2</v>
+      </c>
+      <c r="I441" t="n">
+        <v>3</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="n">
+        <v>1</v>
+      </c>
+      <c r="L441" t="n">
+        <v>1</v>
+      </c>
+      <c r="M441" t="n">
+        <v>1</v>
+      </c>
+      <c r="N441" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>FLOR DE LIZ</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>MALDONADO LOZANO</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>5 C</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>16</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>1</v>
+      </c>
+      <c r="H442" t="n">
+        <v>1</v>
+      </c>
+      <c r="I442" t="n">
+        <v>3</v>
+      </c>
+      <c r="J442" t="n">
+        <v>3</v>
+      </c>
+      <c r="K442" t="n">
+        <v>3</v>
+      </c>
+      <c r="L442" t="n">
+        <v>3</v>
+      </c>
+      <c r="M442" t="n">
+        <v>3</v>
+      </c>
+      <c r="N442" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" t="n">
+        <v>1</v>
+      </c>
+      <c r="P442" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>kiaravalentina</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>VASQUEZ ZURITA</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>5to C</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>17</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>1</v>
+      </c>
+      <c r="H443" t="n">
+        <v>1</v>
+      </c>
+      <c r="I443" t="n">
+        <v>3</v>
+      </c>
+      <c r="J443" t="n">
+        <v>1</v>
+      </c>
+      <c r="K443" t="n">
+        <v>1</v>
+      </c>
+      <c r="L443" t="n">
+        <v>1</v>
+      </c>
+      <c r="M443" t="n">
+        <v>2</v>
+      </c>
+      <c r="N443" t="n">
+        <v>1</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>piero alexander</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>bustamante</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>5toc</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>17</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>2</v>
+      </c>
+      <c r="H444" t="n">
+        <v>1</v>
+      </c>
+      <c r="I444" t="n">
+        <v>1</v>
+      </c>
+      <c r="J444" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" t="n">
+        <v>2</v>
+      </c>
+      <c r="M444" t="n">
+        <v>1</v>
+      </c>
+      <c r="N444" t="n">
+        <v>1</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mauricio carlos </t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ponce </t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>5 B Secundaria</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>16</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>1</v>
+      </c>
+      <c r="H445" t="n">
+        <v>1</v>
+      </c>
+      <c r="I445" t="n">
+        <v>1</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0</v>
+      </c>
+      <c r="K445" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" t="n">
+        <v>1</v>
+      </c>
+      <c r="M445" t="n">
+        <v>1</v>
+      </c>
+      <c r="N445" t="n">
+        <v>1</v>
+      </c>
+      <c r="O445" t="n">
+        <v>1</v>
+      </c>
+      <c r="P445" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Luis Zenobio</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Del Pino Ascona</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>5to C</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>17</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>1</v>
+      </c>
+      <c r="H446" t="n">
+        <v>1</v>
+      </c>
+      <c r="I446" t="n">
+        <v>2</v>
+      </c>
+      <c r="J446" t="n">
+        <v>1</v>
+      </c>
+      <c r="K446" t="n">
+        <v>2</v>
+      </c>
+      <c r="L446" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" t="n">
+        <v>2</v>
+      </c>
+      <c r="N446" t="n">
+        <v>1</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>JUAN MOISES</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>MORI DORDAN</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>5 C</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>17</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>2</v>
+      </c>
+      <c r="H447" t="n">
+        <v>2</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1</v>
+      </c>
+      <c r="J447" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" t="n">
+        <v>0</v>
+      </c>
+      <c r="M447" t="n">
+        <v>2</v>
+      </c>
+      <c r="N447" t="n">
+        <v>2</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>leonardo fabiano A</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>flores</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>5to C</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>17</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>1</v>
+      </c>
+      <c r="H448" t="n">
+        <v>1</v>
+      </c>
+      <c r="I448" t="n">
+        <v>1</v>
+      </c>
+      <c r="J448" t="n">
+        <v>2</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L448" t="n">
+        <v>1</v>
+      </c>
+      <c r="M448" t="n">
+        <v>1</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="P448" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angel alexander </t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>huamani sarmiento</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>13</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>0</v>
+      </c>
+      <c r="H449" t="n">
+        <v>1</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="n">
+        <v>0</v>
+      </c>
+      <c r="K449" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" t="n">
+        <v>2</v>
+      </c>
+      <c r="M449" t="n">
+        <v>2</v>
+      </c>
+      <c r="N449" t="n">
+        <v>3</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+      <c r="P449" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daleshka Estefania </t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amoretti La Rosa </t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>14</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>1</v>
+      </c>
+      <c r="H450" t="n">
+        <v>1</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="n">
+        <v>1</v>
+      </c>
+      <c r="L450" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" t="n">
+        <v>1</v>
+      </c>
+      <c r="N450" t="n">
+        <v>1</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="P450" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaori Meilyn </t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Flores Yupanqui</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>14</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>1</v>
+      </c>
+      <c r="H451" t="n">
+        <v>1</v>
+      </c>
+      <c r="I451" t="n">
+        <v>3</v>
+      </c>
+      <c r="J451" t="n">
+        <v>1</v>
+      </c>
+      <c r="K451" t="n">
+        <v>2</v>
+      </c>
+      <c r="L451" t="n">
+        <v>0</v>
+      </c>
+      <c r="M451" t="n">
+        <v>1</v>
+      </c>
+      <c r="N451" t="n">
+        <v>1</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Jean Franco</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Torres paredes </t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>14</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>1</v>
+      </c>
+      <c r="H452" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" t="n">
+        <v>1</v>
+      </c>
+      <c r="J452" t="n">
+        <v>2</v>
+      </c>
+      <c r="K452" t="n">
+        <v>1</v>
+      </c>
+      <c r="L452" t="n">
+        <v>0</v>
+      </c>
+      <c r="M452" t="n">
+        <v>2</v>
+      </c>
+      <c r="N452" t="n">
+        <v>1</v>
+      </c>
+      <c r="O452" t="n">
+        <v>0</v>
+      </c>
+      <c r="P452" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>luana cristel maria</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>colonio loli</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>14</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>1</v>
+      </c>
+      <c r="H453" t="n">
+        <v>1</v>
+      </c>
+      <c r="I453" t="n">
+        <v>2</v>
+      </c>
+      <c r="J453" t="n">
+        <v>1</v>
+      </c>
+      <c r="K453" t="n">
+        <v>1</v>
+      </c>
+      <c r="L453" t="n">
+        <v>1</v>
+      </c>
+      <c r="M453" t="n">
+        <v>1</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>1</v>
+      </c>
+      <c r="P453" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>kaori dayanara</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>castillo burneo</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2doB</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>14</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>1</v>
+      </c>
+      <c r="H454" t="n">
+        <v>1</v>
+      </c>
+      <c r="I454" t="n">
+        <v>2</v>
+      </c>
+      <c r="J454" t="n">
+        <v>1</v>
+      </c>
+      <c r="K454" t="n">
+        <v>0</v>
+      </c>
+      <c r="L454" t="n">
+        <v>1</v>
+      </c>
+      <c r="M454" t="n">
+        <v>1</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
+      <c r="P454" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>yaraby sarai</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>fasabi machoa</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>14</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>1</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0</v>
+      </c>
+      <c r="I455" t="n">
+        <v>1</v>
+      </c>
+      <c r="J455" t="n">
+        <v>2</v>
+      </c>
+      <c r="K455" t="n">
+        <v>2</v>
+      </c>
+      <c r="L455" t="n">
+        <v>1</v>
+      </c>
+      <c r="M455" t="n">
+        <v>2</v>
+      </c>
+      <c r="N455" t="n">
+        <v>1</v>
+      </c>
+      <c r="O455" t="n">
+        <v>3</v>
+      </c>
+      <c r="P455" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>cris gerald</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>panaifo</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>14</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>1</v>
+      </c>
+      <c r="H456" t="n">
+        <v>1</v>
+      </c>
+      <c r="I456" t="n">
+        <v>2</v>
+      </c>
+      <c r="J456" t="n">
+        <v>1</v>
+      </c>
+      <c r="K456" t="n">
+        <v>0</v>
+      </c>
+      <c r="L456" t="n">
+        <v>1</v>
+      </c>
+      <c r="M456" t="n">
+        <v>1</v>
+      </c>
+      <c r="N456" t="n">
+        <v>2</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>dominic</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>anguash sanchez</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>14</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>1</v>
+      </c>
+      <c r="H457" t="n">
+        <v>1</v>
+      </c>
+      <c r="I457" t="n">
+        <v>3</v>
+      </c>
+      <c r="J457" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0</v>
+      </c>
+      <c r="L457" t="n">
+        <v>1</v>
+      </c>
+      <c r="M457" t="n">
+        <v>1</v>
+      </c>
+      <c r="N457" t="n">
+        <v>1</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0</v>
+      </c>
+      <c r="P457" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>jorge luis</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>muñoz armestar</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2doB</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>14</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>1</v>
+      </c>
+      <c r="H458" t="n">
+        <v>2</v>
+      </c>
+      <c r="I458" t="n">
+        <v>1</v>
+      </c>
+      <c r="J458" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" t="n">
+        <v>1</v>
+      </c>
+      <c r="L458" t="n">
+        <v>0</v>
+      </c>
+      <c r="M458" t="n">
+        <v>2</v>
+      </c>
+      <c r="N458" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+      <c r="P458" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Donovan Fabiano</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>valverde castro</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2 b</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>15</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" t="n">
+        <v>1</v>
+      </c>
+      <c r="I459" t="n">
+        <v>3</v>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>1</v>
+      </c>
+      <c r="L459" t="n">
+        <v>1</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0</v>
+      </c>
+      <c r="N459" t="n">
+        <v>2</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italo Agustin </t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herrera </t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>14</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>0</v>
+      </c>
+      <c r="H460" t="n">
+        <v>1</v>
+      </c>
+      <c r="I460" t="n">
+        <v>1</v>
+      </c>
+      <c r="J460" t="n">
+        <v>1</v>
+      </c>
+      <c r="K460" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" t="n">
+        <v>0</v>
+      </c>
+      <c r="M460" t="n">
+        <v>3</v>
+      </c>
+      <c r="N460" t="n">
+        <v>1</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+      <c r="P460" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>poma</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>14</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>1</v>
+      </c>
+      <c r="H461" t="n">
+        <v>2</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J461" t="n">
+        <v>1</v>
+      </c>
+      <c r="K461" t="n">
+        <v>0</v>
+      </c>
+      <c r="L461" t="n">
+        <v>0</v>
+      </c>
+      <c r="M461" t="n">
+        <v>1</v>
+      </c>
+      <c r="N461" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="P461" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>axl alvarado</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>ortiz</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>14</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>1</v>
+      </c>
+      <c r="H462" t="n">
+        <v>2</v>
+      </c>
+      <c r="I462" t="n">
+        <v>2</v>
+      </c>
+      <c r="J462" t="n">
+        <v>1</v>
+      </c>
+      <c r="K462" t="n">
+        <v>1</v>
+      </c>
+      <c r="L462" t="n">
+        <v>3</v>
+      </c>
+      <c r="M462" t="n">
+        <v>1</v>
+      </c>
+      <c r="N462" t="n">
+        <v>1</v>
+      </c>
+      <c r="O462" t="n">
+        <v>1</v>
+      </c>
+      <c r="P462" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>zoe ariana</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>agurto</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>14</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>1</v>
+      </c>
+      <c r="H463" t="n">
+        <v>1</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0</v>
+      </c>
+      <c r="J463" t="n">
+        <v>2</v>
+      </c>
+      <c r="K463" t="n">
+        <v>2</v>
+      </c>
+      <c r="L463" t="n">
+        <v>1</v>
+      </c>
+      <c r="M463" t="n">
+        <v>1</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0</v>
+      </c>
+      <c r="P463" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Adriano Sebastian</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Reyna Aguilar</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>14</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>1</v>
+      </c>
+      <c r="H464" t="n">
+        <v>1</v>
+      </c>
+      <c r="I464" t="n">
+        <v>1</v>
+      </c>
+      <c r="J464" t="n">
+        <v>1</v>
+      </c>
+      <c r="K464" t="n">
+        <v>2</v>
+      </c>
+      <c r="L464" t="n">
+        <v>1</v>
+      </c>
+      <c r="M464" t="n">
+        <v>1</v>
+      </c>
+      <c r="N464" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>alexis ignacio</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>soto</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2do B</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>12</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>0</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" t="n">
+        <v>1</v>
+      </c>
+      <c r="K465" t="n">
+        <v>1</v>
+      </c>
+      <c r="L465" t="n">
+        <v>2</v>
+      </c>
+      <c r="M465" t="n">
+        <v>2</v>
+      </c>
+      <c r="N465" t="n">
+        <v>0</v>
+      </c>
+      <c r="O465" t="n">
+        <v>1</v>
+      </c>
+      <c r="P465" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crudo/Test_inicial.xlsx
+++ b/data/crudo/Test_inicial.xlsx
@@ -20330,7 +20330,7 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -21695,7 +21695,7 @@
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -22410,7 +22410,7 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -22605,7 +22605,7 @@
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -22735,7 +22735,7 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -23450,7 +23450,7 @@
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -23905,7 +23905,7 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -24620,7 +24620,7 @@
       </c>
       <c r="Q372" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -25010,7 +25010,7 @@
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -25205,7 +25205,7 @@
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -25465,7 +25465,7 @@
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="Q398" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>Minimo</t>
+          <t>Mínimo</t>
         </is>
       </c>
     </row>

--- a/data/crudo/Test_inicial.xlsx
+++ b/data/crudo/Test_inicial.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q465"/>
+  <dimension ref="A1:Q583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30669,6 +30669,7676 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>FERNANDA</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>PALOMINO</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>5TO</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>17</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>2</v>
+      </c>
+      <c r="H466" t="n">
+        <v>2</v>
+      </c>
+      <c r="I466" t="n">
+        <v>1</v>
+      </c>
+      <c r="J466" t="n">
+        <v>3</v>
+      </c>
+      <c r="K466" t="n">
+        <v>1</v>
+      </c>
+      <c r="L466" t="n">
+        <v>0</v>
+      </c>
+      <c r="M466" t="n">
+        <v>1</v>
+      </c>
+      <c r="N466" t="n">
+        <v>1</v>
+      </c>
+      <c r="O466" t="n">
+        <v>0</v>
+      </c>
+      <c r="P466" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>16</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>1</v>
+      </c>
+      <c r="H467" t="n">
+        <v>1</v>
+      </c>
+      <c r="I467" t="n">
+        <v>2</v>
+      </c>
+      <c r="J467" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" t="n">
+        <v>1</v>
+      </c>
+      <c r="L467" t="n">
+        <v>0</v>
+      </c>
+      <c r="M467" t="n">
+        <v>0</v>
+      </c>
+      <c r="N467" t="n">
+        <v>1</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
+      <c r="P467" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Xiomara</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Tarazona</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>16</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>1</v>
+      </c>
+      <c r="H468" t="n">
+        <v>2</v>
+      </c>
+      <c r="I468" t="n">
+        <v>1</v>
+      </c>
+      <c r="J468" t="n">
+        <v>0</v>
+      </c>
+      <c r="K468" t="n">
+        <v>1</v>
+      </c>
+      <c r="L468" t="n">
+        <v>1</v>
+      </c>
+      <c r="M468" t="n">
+        <v>3</v>
+      </c>
+      <c r="N468" t="n">
+        <v>1</v>
+      </c>
+      <c r="O468" t="n">
+        <v>1</v>
+      </c>
+      <c r="P468" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Arista</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>17</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>1</v>
+      </c>
+      <c r="H469" t="n">
+        <v>1</v>
+      </c>
+      <c r="I469" t="n">
+        <v>1</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1</v>
+      </c>
+      <c r="K469" t="n">
+        <v>1</v>
+      </c>
+      <c r="L469" t="n">
+        <v>1</v>
+      </c>
+      <c r="M469" t="n">
+        <v>1</v>
+      </c>
+      <c r="N469" t="n">
+        <v>1</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">luciana noelia </t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>obregon</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>5secu</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>16</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G470" t="n">
+        <v>1</v>
+      </c>
+      <c r="H470" t="n">
+        <v>1</v>
+      </c>
+      <c r="I470" t="n">
+        <v>1</v>
+      </c>
+      <c r="J470" t="n">
+        <v>1</v>
+      </c>
+      <c r="K470" t="n">
+        <v>1</v>
+      </c>
+      <c r="L470" t="n">
+        <v>1</v>
+      </c>
+      <c r="M470" t="n">
+        <v>1</v>
+      </c>
+      <c r="N470" t="n">
+        <v>1</v>
+      </c>
+      <c r="O470" t="n">
+        <v>0</v>
+      </c>
+      <c r="P470" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Vania Adriana</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Ardiles</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>5sec</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>17</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G471" t="n">
+        <v>1</v>
+      </c>
+      <c r="H471" t="n">
+        <v>3</v>
+      </c>
+      <c r="I471" t="n">
+        <v>2</v>
+      </c>
+      <c r="J471" t="n">
+        <v>1</v>
+      </c>
+      <c r="K471" t="n">
+        <v>1</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" t="n">
+        <v>1</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="P471" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>cely</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>uturunco</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>16</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G472" t="n">
+        <v>1</v>
+      </c>
+      <c r="H472" t="n">
+        <v>2</v>
+      </c>
+      <c r="I472" t="n">
+        <v>1</v>
+      </c>
+      <c r="J472" t="n">
+        <v>1</v>
+      </c>
+      <c r="K472" t="n">
+        <v>0</v>
+      </c>
+      <c r="L472" t="n">
+        <v>1</v>
+      </c>
+      <c r="M472" t="n">
+        <v>0</v>
+      </c>
+      <c r="N472" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" t="n">
+        <v>1</v>
+      </c>
+      <c r="P472" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Nehemías Fermín</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Salas Uchuya</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>5to A</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>17</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G473" t="n">
+        <v>1</v>
+      </c>
+      <c r="H473" t="n">
+        <v>2</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+      <c r="J473" t="n">
+        <v>1</v>
+      </c>
+      <c r="K473" t="n">
+        <v>1</v>
+      </c>
+      <c r="L473" t="n">
+        <v>2</v>
+      </c>
+      <c r="M473" t="n">
+        <v>3</v>
+      </c>
+      <c r="N473" t="n">
+        <v>1</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>rodrigo jose</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>zambrano chavez</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>16</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G474" t="n">
+        <v>1</v>
+      </c>
+      <c r="H474" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1</v>
+      </c>
+      <c r="J474" t="n">
+        <v>2</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="n">
+        <v>1</v>
+      </c>
+      <c r="M474" t="n">
+        <v>2</v>
+      </c>
+      <c r="N474" t="n">
+        <v>1</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Almendra</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>tarrillo</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>16</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G475" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" t="n">
+        <v>1</v>
+      </c>
+      <c r="I475" t="n">
+        <v>2</v>
+      </c>
+      <c r="J475" t="n">
+        <v>1</v>
+      </c>
+      <c r="K475" t="n">
+        <v>1</v>
+      </c>
+      <c r="L475" t="n">
+        <v>1</v>
+      </c>
+      <c r="M475" t="n">
+        <v>3</v>
+      </c>
+      <c r="N475" t="n">
+        <v>1</v>
+      </c>
+      <c r="O475" t="n">
+        <v>1</v>
+      </c>
+      <c r="P475" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>ADIEL</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>HUARCAYA</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>17</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G476" t="n">
+        <v>0</v>
+      </c>
+      <c r="H476" t="n">
+        <v>1</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="n">
+        <v>1</v>
+      </c>
+      <c r="K476" t="n">
+        <v>0</v>
+      </c>
+      <c r="L476" t="n">
+        <v>0</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0</v>
+      </c>
+      <c r="N476" t="n">
+        <v>1</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kiara </t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Flores Campos</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>17</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G477" t="n">
+        <v>2</v>
+      </c>
+      <c r="H477" t="n">
+        <v>2</v>
+      </c>
+      <c r="I477" t="n">
+        <v>1</v>
+      </c>
+      <c r="J477" t="n">
+        <v>3</v>
+      </c>
+      <c r="K477" t="n">
+        <v>2</v>
+      </c>
+      <c r="L477" t="n">
+        <v>1</v>
+      </c>
+      <c r="M477" t="n">
+        <v>1</v>
+      </c>
+      <c r="N477" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" t="n">
+        <v>1</v>
+      </c>
+      <c r="P477" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>16</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G478" t="n">
+        <v>0</v>
+      </c>
+      <c r="H478" t="n">
+        <v>1</v>
+      </c>
+      <c r="I478" t="n">
+        <v>1</v>
+      </c>
+      <c r="J478" t="n">
+        <v>1</v>
+      </c>
+      <c r="K478" t="n">
+        <v>2</v>
+      </c>
+      <c r="L478" t="n">
+        <v>0</v>
+      </c>
+      <c r="M478" t="n">
+        <v>1</v>
+      </c>
+      <c r="N478" t="n">
+        <v>0</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
+      <c r="P478" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Pieer A</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>giménez</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>16</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G479" t="n">
+        <v>1</v>
+      </c>
+      <c r="H479" t="n">
+        <v>1</v>
+      </c>
+      <c r="I479" t="n">
+        <v>2</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1</v>
+      </c>
+      <c r="K479" t="n">
+        <v>2</v>
+      </c>
+      <c r="L479" t="n">
+        <v>1</v>
+      </c>
+      <c r="M479" t="n">
+        <v>1</v>
+      </c>
+      <c r="N479" t="n">
+        <v>1</v>
+      </c>
+      <c r="O479" t="n">
+        <v>1</v>
+      </c>
+      <c r="P479" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Nayeli</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Silupu</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>16</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G480" t="n">
+        <v>1</v>
+      </c>
+      <c r="H480" t="n">
+        <v>1</v>
+      </c>
+      <c r="I480" t="n">
+        <v>2</v>
+      </c>
+      <c r="J480" t="n">
+        <v>2</v>
+      </c>
+      <c r="K480" t="n">
+        <v>3</v>
+      </c>
+      <c r="L480" t="n">
+        <v>3</v>
+      </c>
+      <c r="M480" t="n">
+        <v>3</v>
+      </c>
+      <c r="N480" t="n">
+        <v>2</v>
+      </c>
+      <c r="O480" t="n">
+        <v>3</v>
+      </c>
+      <c r="P480" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Leonardo D</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Ruiz Rubio</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>5to sec</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>17</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G481" t="n">
+        <v>1</v>
+      </c>
+      <c r="H481" t="n">
+        <v>1</v>
+      </c>
+      <c r="I481" t="n">
+        <v>1</v>
+      </c>
+      <c r="J481" t="n">
+        <v>1</v>
+      </c>
+      <c r="K481" t="n">
+        <v>1</v>
+      </c>
+      <c r="L481" t="n">
+        <v>1</v>
+      </c>
+      <c r="M481" t="n">
+        <v>1</v>
+      </c>
+      <c r="N481" t="n">
+        <v>1</v>
+      </c>
+      <c r="O481" t="n">
+        <v>0</v>
+      </c>
+      <c r="P481" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sthefany nicole </t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavez </t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>5to sec</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>16</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G482" t="n">
+        <v>1</v>
+      </c>
+      <c r="H482" t="n">
+        <v>3</v>
+      </c>
+      <c r="I482" t="n">
+        <v>1</v>
+      </c>
+      <c r="J482" t="n">
+        <v>1</v>
+      </c>
+      <c r="K482" t="n">
+        <v>0</v>
+      </c>
+      <c r="L482" t="n">
+        <v>1</v>
+      </c>
+      <c r="M482" t="n">
+        <v>3</v>
+      </c>
+      <c r="N482" t="n">
+        <v>1</v>
+      </c>
+      <c r="O482" t="n">
+        <v>1</v>
+      </c>
+      <c r="P482" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Lía N</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Marcos Tasayco</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>5to A</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>17</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G483" t="n">
+        <v>2</v>
+      </c>
+      <c r="H483" t="n">
+        <v>1</v>
+      </c>
+      <c r="I483" t="n">
+        <v>1</v>
+      </c>
+      <c r="J483" t="n">
+        <v>1</v>
+      </c>
+      <c r="K483" t="n">
+        <v>2</v>
+      </c>
+      <c r="L483" t="n">
+        <v>2</v>
+      </c>
+      <c r="M483" t="n">
+        <v>1</v>
+      </c>
+      <c r="N483" t="n">
+        <v>1</v>
+      </c>
+      <c r="O483" t="n">
+        <v>1</v>
+      </c>
+      <c r="P483" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Dayana</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sakumoto </t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>16</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G484" t="n">
+        <v>1</v>
+      </c>
+      <c r="H484" t="n">
+        <v>1</v>
+      </c>
+      <c r="I484" t="n">
+        <v>1</v>
+      </c>
+      <c r="J484" t="n">
+        <v>1</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" t="n">
+        <v>1</v>
+      </c>
+      <c r="N484" t="n">
+        <v>0</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Diego A</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Cotrina</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>16</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G485" t="n">
+        <v>1</v>
+      </c>
+      <c r="H485" t="n">
+        <v>1</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" t="n">
+        <v>1</v>
+      </c>
+      <c r="N485" t="n">
+        <v>2</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>william u</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>cruz q</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>17</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G486" t="n">
+        <v>1</v>
+      </c>
+      <c r="H486" t="n">
+        <v>1</v>
+      </c>
+      <c r="I486" t="n">
+        <v>1</v>
+      </c>
+      <c r="J486" t="n">
+        <v>1</v>
+      </c>
+      <c r="K486" t="n">
+        <v>1</v>
+      </c>
+      <c r="L486" t="n">
+        <v>0</v>
+      </c>
+      <c r="M486" t="n">
+        <v>1</v>
+      </c>
+      <c r="N486" t="n">
+        <v>1</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="P486" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>jayded Del Pilar</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>santisteban lopez</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>17</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G487" t="n">
+        <v>2</v>
+      </c>
+      <c r="H487" t="n">
+        <v>2</v>
+      </c>
+      <c r="I487" t="n">
+        <v>1</v>
+      </c>
+      <c r="J487" t="n">
+        <v>3</v>
+      </c>
+      <c r="K487" t="n">
+        <v>1</v>
+      </c>
+      <c r="L487" t="n">
+        <v>3</v>
+      </c>
+      <c r="M487" t="n">
+        <v>3</v>
+      </c>
+      <c r="N487" t="n">
+        <v>1</v>
+      </c>
+      <c r="O487" t="n">
+        <v>1</v>
+      </c>
+      <c r="P487" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>victor fernando</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>paredes chero</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>17</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G488" t="n">
+        <v>1</v>
+      </c>
+      <c r="H488" t="n">
+        <v>2</v>
+      </c>
+      <c r="I488" t="n">
+        <v>2</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1</v>
+      </c>
+      <c r="K488" t="n">
+        <v>1</v>
+      </c>
+      <c r="L488" t="n">
+        <v>1</v>
+      </c>
+      <c r="M488" t="n">
+        <v>1</v>
+      </c>
+      <c r="N488" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Tomas L</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Loza</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>17</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G489" t="n">
+        <v>2</v>
+      </c>
+      <c r="H489" t="n">
+        <v>1</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1</v>
+      </c>
+      <c r="J489" t="n">
+        <v>2</v>
+      </c>
+      <c r="K489" t="n">
+        <v>2</v>
+      </c>
+      <c r="L489" t="n">
+        <v>3</v>
+      </c>
+      <c r="M489" t="n">
+        <v>2</v>
+      </c>
+      <c r="N489" t="n">
+        <v>1</v>
+      </c>
+      <c r="O489" t="n">
+        <v>1</v>
+      </c>
+      <c r="P489" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>paolo david</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>paiva</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>17</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G490" t="n">
+        <v>1</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>2</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
+      <c r="P490" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Millely A</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Perez Mosqueira</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>5to</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>16</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>3</v>
+      </c>
+      <c r="H491" t="n">
+        <v>1</v>
+      </c>
+      <c r="I491" t="n">
+        <v>3</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2</v>
+      </c>
+      <c r="K491" t="n">
+        <v>3</v>
+      </c>
+      <c r="L491" t="n">
+        <v>2</v>
+      </c>
+      <c r="M491" t="n">
+        <v>3</v>
+      </c>
+      <c r="N491" t="n">
+        <v>1</v>
+      </c>
+      <c r="O491" t="n">
+        <v>1</v>
+      </c>
+      <c r="P491" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>4secu</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>15</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G492" t="n">
+        <v>1</v>
+      </c>
+      <c r="H492" t="n">
+        <v>1</v>
+      </c>
+      <c r="I492" t="n">
+        <v>1</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>1</v>
+      </c>
+      <c r="L492" t="n">
+        <v>2</v>
+      </c>
+      <c r="M492" t="n">
+        <v>1</v>
+      </c>
+      <c r="N492" t="n">
+        <v>0</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Aleshka Victoria</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Giacomotti Francia</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>4 to</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>15</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>1</v>
+      </c>
+      <c r="H493" t="n">
+        <v>1</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>1</v>
+      </c>
+      <c r="K493" t="n">
+        <v>1</v>
+      </c>
+      <c r="L493" t="n">
+        <v>1</v>
+      </c>
+      <c r="M493" t="n">
+        <v>2</v>
+      </c>
+      <c r="N493" t="n">
+        <v>1</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Alonso Santiago</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Guzmán Navarro</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>16</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>2</v>
+      </c>
+      <c r="H494" t="n">
+        <v>1</v>
+      </c>
+      <c r="I494" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" t="n">
+        <v>2</v>
+      </c>
+      <c r="K494" t="n">
+        <v>1</v>
+      </c>
+      <c r="L494" t="n">
+        <v>2</v>
+      </c>
+      <c r="M494" t="n">
+        <v>2</v>
+      </c>
+      <c r="N494" t="n">
+        <v>2</v>
+      </c>
+      <c r="O494" t="n">
+        <v>2</v>
+      </c>
+      <c r="P494" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Kiare</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Sandon</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>16</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>1</v>
+      </c>
+      <c r="H495" t="n">
+        <v>1</v>
+      </c>
+      <c r="I495" t="n">
+        <v>2</v>
+      </c>
+      <c r="J495" t="n">
+        <v>1</v>
+      </c>
+      <c r="K495" t="n">
+        <v>1</v>
+      </c>
+      <c r="L495" t="n">
+        <v>1</v>
+      </c>
+      <c r="M495" t="n">
+        <v>1</v>
+      </c>
+      <c r="N495" t="n">
+        <v>1</v>
+      </c>
+      <c r="O495" t="n">
+        <v>1</v>
+      </c>
+      <c r="P495" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Jairo Richard</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Aguilar Leon</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>16</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>2</v>
+      </c>
+      <c r="H496" t="n">
+        <v>2</v>
+      </c>
+      <c r="I496" t="n">
+        <v>2</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1</v>
+      </c>
+      <c r="K496" t="n">
+        <v>1</v>
+      </c>
+      <c r="L496" t="n">
+        <v>0</v>
+      </c>
+      <c r="M496" t="n">
+        <v>1</v>
+      </c>
+      <c r="N496" t="n">
+        <v>1</v>
+      </c>
+      <c r="O496" t="n">
+        <v>3</v>
+      </c>
+      <c r="P496" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Luis Andree</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Sandoval Vilegas</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>15</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>2</v>
+      </c>
+      <c r="H497" t="n">
+        <v>1</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1</v>
+      </c>
+      <c r="J497" t="n">
+        <v>2</v>
+      </c>
+      <c r="K497" t="n">
+        <v>1</v>
+      </c>
+      <c r="L497" t="n">
+        <v>1</v>
+      </c>
+      <c r="M497" t="n">
+        <v>2</v>
+      </c>
+      <c r="N497" t="n">
+        <v>1</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Antonella</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Bailetty</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>4to secundaria</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>16</v>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G498" t="n">
+        <v>1</v>
+      </c>
+      <c r="H498" t="n">
+        <v>1</v>
+      </c>
+      <c r="I498" t="n">
+        <v>2</v>
+      </c>
+      <c r="J498" t="n">
+        <v>1</v>
+      </c>
+      <c r="K498" t="n">
+        <v>2</v>
+      </c>
+      <c r="L498" t="n">
+        <v>0</v>
+      </c>
+      <c r="M498" t="n">
+        <v>1</v>
+      </c>
+      <c r="N498" t="n">
+        <v>1</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
+      <c r="P498" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Sahariana Rossy</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Ruiz Rodriguez</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>4to secundaria</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>15</v>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G499" t="n">
+        <v>1</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" t="n">
+        <v>3</v>
+      </c>
+      <c r="J499" t="n">
+        <v>2</v>
+      </c>
+      <c r="K499" t="n">
+        <v>2</v>
+      </c>
+      <c r="L499" t="n">
+        <v>1</v>
+      </c>
+      <c r="M499" t="n">
+        <v>1</v>
+      </c>
+      <c r="N499" t="n">
+        <v>1</v>
+      </c>
+      <c r="O499" t="n">
+        <v>1</v>
+      </c>
+      <c r="P499" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Romina Paola</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Uculmana</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>15</v>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>3</v>
+      </c>
+      <c r="H500" t="n">
+        <v>2</v>
+      </c>
+      <c r="I500" t="n">
+        <v>1</v>
+      </c>
+      <c r="J500" t="n">
+        <v>2</v>
+      </c>
+      <c r="K500" t="n">
+        <v>1</v>
+      </c>
+      <c r="L500" t="n">
+        <v>3</v>
+      </c>
+      <c r="M500" t="n">
+        <v>1</v>
+      </c>
+      <c r="N500" t="n">
+        <v>1</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Alessandra V</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Perez Trejo</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>15</v>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G501" t="n">
+        <v>2</v>
+      </c>
+      <c r="H501" t="n">
+        <v>1</v>
+      </c>
+      <c r="I501" t="n">
+        <v>3</v>
+      </c>
+      <c r="J501" t="n">
+        <v>1</v>
+      </c>
+      <c r="K501" t="n">
+        <v>0</v>
+      </c>
+      <c r="L501" t="n">
+        <v>1</v>
+      </c>
+      <c r="M501" t="n">
+        <v>1</v>
+      </c>
+      <c r="N501" t="n">
+        <v>1</v>
+      </c>
+      <c r="O501" t="n">
+        <v>1</v>
+      </c>
+      <c r="P501" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Ivana Luana</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Ponce</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>16</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G502" t="n">
+        <v>3</v>
+      </c>
+      <c r="H502" t="n">
+        <v>2</v>
+      </c>
+      <c r="I502" t="n">
+        <v>3</v>
+      </c>
+      <c r="J502" t="n">
+        <v>3</v>
+      </c>
+      <c r="K502" t="n">
+        <v>1</v>
+      </c>
+      <c r="L502" t="n">
+        <v>2</v>
+      </c>
+      <c r="M502" t="n">
+        <v>3</v>
+      </c>
+      <c r="N502" t="n">
+        <v>3</v>
+      </c>
+      <c r="O502" t="n">
+        <v>2</v>
+      </c>
+      <c r="P502" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Luana Ivana</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Caro</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>15</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G503" t="n">
+        <v>3</v>
+      </c>
+      <c r="H503" t="n">
+        <v>1</v>
+      </c>
+      <c r="I503" t="n">
+        <v>3</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" t="n">
+        <v>2</v>
+      </c>
+      <c r="M503" t="n">
+        <v>1</v>
+      </c>
+      <c r="N503" t="n">
+        <v>0</v>
+      </c>
+      <c r="O503" t="n">
+        <v>1</v>
+      </c>
+      <c r="P503" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Edward I</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Conche Huaynates</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>15</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>1</v>
+      </c>
+      <c r="I504" t="n">
+        <v>1</v>
+      </c>
+      <c r="J504" t="n">
+        <v>1</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="n">
+        <v>0</v>
+      </c>
+      <c r="M504" t="n">
+        <v>1</v>
+      </c>
+      <c r="N504" t="n">
+        <v>1</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Belen Judith</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Ordoñez</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>16</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G505" t="n">
+        <v>1</v>
+      </c>
+      <c r="H505" t="n">
+        <v>1</v>
+      </c>
+      <c r="I505" t="n">
+        <v>1</v>
+      </c>
+      <c r="J505" t="n">
+        <v>2</v>
+      </c>
+      <c r="K505" t="n">
+        <v>1</v>
+      </c>
+      <c r="L505" t="n">
+        <v>1</v>
+      </c>
+      <c r="M505" t="n">
+        <v>1</v>
+      </c>
+      <c r="N505" t="n">
+        <v>1</v>
+      </c>
+      <c r="O505" t="n">
+        <v>1</v>
+      </c>
+      <c r="P505" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Mathias S</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Sánchez Salas</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>16</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G506" t="n">
+        <v>1</v>
+      </c>
+      <c r="H506" t="n">
+        <v>1</v>
+      </c>
+      <c r="I506" t="n">
+        <v>2</v>
+      </c>
+      <c r="J506" t="n">
+        <v>2</v>
+      </c>
+      <c r="K506" t="n">
+        <v>0</v>
+      </c>
+      <c r="L506" t="n">
+        <v>0</v>
+      </c>
+      <c r="M506" t="n">
+        <v>1</v>
+      </c>
+      <c r="N506" t="n">
+        <v>0</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Dayla R</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Reyes Saldarriaga</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>16</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G507" t="n">
+        <v>2</v>
+      </c>
+      <c r="H507" t="n">
+        <v>3</v>
+      </c>
+      <c r="I507" t="n">
+        <v>1</v>
+      </c>
+      <c r="J507" t="n">
+        <v>3</v>
+      </c>
+      <c r="K507" t="n">
+        <v>3</v>
+      </c>
+      <c r="L507" t="n">
+        <v>3</v>
+      </c>
+      <c r="M507" t="n">
+        <v>3</v>
+      </c>
+      <c r="N507" t="n">
+        <v>1</v>
+      </c>
+      <c r="O507" t="n">
+        <v>2</v>
+      </c>
+      <c r="P507" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Kevin Fernando</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Arbulú Bellodas</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>4toB</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>15</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G508" t="n">
+        <v>1</v>
+      </c>
+      <c r="H508" t="n">
+        <v>1</v>
+      </c>
+      <c r="I508" t="n">
+        <v>1</v>
+      </c>
+      <c r="J508" t="n">
+        <v>1</v>
+      </c>
+      <c r="K508" t="n">
+        <v>0</v>
+      </c>
+      <c r="L508" t="n">
+        <v>0</v>
+      </c>
+      <c r="M508" t="n">
+        <v>1</v>
+      </c>
+      <c r="N508" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Jimena F</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>15</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G509" t="n">
+        <v>1</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" t="n">
+        <v>1</v>
+      </c>
+      <c r="M509" t="n">
+        <v>1</v>
+      </c>
+      <c r="N509" t="n">
+        <v>2</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Kiara M</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Montenegro D</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>16</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>1</v>
+      </c>
+      <c r="H510" t="n">
+        <v>1</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1</v>
+      </c>
+      <c r="J510" t="n">
+        <v>2</v>
+      </c>
+      <c r="K510" t="n">
+        <v>2</v>
+      </c>
+      <c r="L510" t="n">
+        <v>2</v>
+      </c>
+      <c r="M510" t="n">
+        <v>2</v>
+      </c>
+      <c r="N510" t="n">
+        <v>1</v>
+      </c>
+      <c r="O510" t="n">
+        <v>2</v>
+      </c>
+      <c r="P510" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Alanis L</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Zevallos Saavedra</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>4to B</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>16</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G511" t="n">
+        <v>1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>1</v>
+      </c>
+      <c r="I511" t="n">
+        <v>1</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" t="n">
+        <v>1</v>
+      </c>
+      <c r="N511" t="n">
+        <v>0</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Asthon Dominick</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Ciezza Rabanal</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>16</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G512" t="n">
+        <v>1</v>
+      </c>
+      <c r="H512" t="n">
+        <v>2</v>
+      </c>
+      <c r="I512" t="n">
+        <v>2</v>
+      </c>
+      <c r="J512" t="n">
+        <v>1</v>
+      </c>
+      <c r="K512" t="n">
+        <v>1</v>
+      </c>
+      <c r="L512" t="n">
+        <v>1</v>
+      </c>
+      <c r="M512" t="n">
+        <v>2</v>
+      </c>
+      <c r="N512" t="n">
+        <v>3</v>
+      </c>
+      <c r="O512" t="n">
+        <v>0</v>
+      </c>
+      <c r="P512" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Adriana A</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>15</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G513" t="n">
+        <v>1</v>
+      </c>
+      <c r="H513" t="n">
+        <v>1</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="n">
+        <v>2</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" t="n">
+        <v>2</v>
+      </c>
+      <c r="M513" t="n">
+        <v>1</v>
+      </c>
+      <c r="N513" t="n">
+        <v>1</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fatima luciana </t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>maza ruiz</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>16</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G514" t="n">
+        <v>2</v>
+      </c>
+      <c r="H514" t="n">
+        <v>1</v>
+      </c>
+      <c r="I514" t="n">
+        <v>3</v>
+      </c>
+      <c r="J514" t="n">
+        <v>2</v>
+      </c>
+      <c r="K514" t="n">
+        <v>1</v>
+      </c>
+      <c r="L514" t="n">
+        <v>1</v>
+      </c>
+      <c r="M514" t="n">
+        <v>1</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Marcelo Mikael</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Macedo</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>4to B</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>16</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>1</v>
+      </c>
+      <c r="H515" t="n">
+        <v>2</v>
+      </c>
+      <c r="I515" t="n">
+        <v>1</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" t="n">
+        <v>1</v>
+      </c>
+      <c r="L515" t="n">
+        <v>1</v>
+      </c>
+      <c r="M515" t="n">
+        <v>1</v>
+      </c>
+      <c r="N515" t="n">
+        <v>1</v>
+      </c>
+      <c r="O515" t="n">
+        <v>1</v>
+      </c>
+      <c r="P515" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Kate Evangeline</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Arana Gavilán</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>15</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>1</v>
+      </c>
+      <c r="H516" t="n">
+        <v>1</v>
+      </c>
+      <c r="I516" t="n">
+        <v>2</v>
+      </c>
+      <c r="J516" t="n">
+        <v>2</v>
+      </c>
+      <c r="K516" t="n">
+        <v>3</v>
+      </c>
+      <c r="L516" t="n">
+        <v>1</v>
+      </c>
+      <c r="M516" t="n">
+        <v>3</v>
+      </c>
+      <c r="N516" t="n">
+        <v>1</v>
+      </c>
+      <c r="O516" t="n">
+        <v>3</v>
+      </c>
+      <c r="P516" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Valeria M</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Mostacero</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>4 año</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>16</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>1</v>
+      </c>
+      <c r="H517" t="n">
+        <v>1</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1</v>
+      </c>
+      <c r="J517" t="n">
+        <v>2</v>
+      </c>
+      <c r="K517" t="n">
+        <v>1</v>
+      </c>
+      <c r="L517" t="n">
+        <v>2</v>
+      </c>
+      <c r="M517" t="n">
+        <v>1</v>
+      </c>
+      <c r="N517" t="n">
+        <v>1</v>
+      </c>
+      <c r="O517" t="n">
+        <v>1</v>
+      </c>
+      <c r="P517" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Gianella</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Chanca</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>4to B</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>16</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>1</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" t="n">
+        <v>1</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0</v>
+      </c>
+      <c r="M518" t="n">
+        <v>0</v>
+      </c>
+      <c r="N518" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Luis D</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Du</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>16</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>1</v>
+      </c>
+      <c r="H519" t="n">
+        <v>0</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" t="n">
+        <v>0</v>
+      </c>
+      <c r="M519" t="n">
+        <v>0</v>
+      </c>
+      <c r="N519" t="n">
+        <v>0</v>
+      </c>
+      <c r="O519" t="n">
+        <v>0</v>
+      </c>
+      <c r="P519" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Paulho S</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>OBesso Quintos</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>16</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G520" t="n">
+        <v>1</v>
+      </c>
+      <c r="H520" t="n">
+        <v>1</v>
+      </c>
+      <c r="I520" t="n">
+        <v>1</v>
+      </c>
+      <c r="J520" t="n">
+        <v>1</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" t="n">
+        <v>1</v>
+      </c>
+      <c r="M520" t="n">
+        <v>2</v>
+      </c>
+      <c r="N520" t="n">
+        <v>1</v>
+      </c>
+      <c r="O520" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>shantal l</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>diaz cortegana</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>15</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>2</v>
+      </c>
+      <c r="H521" t="n">
+        <v>1</v>
+      </c>
+      <c r="I521" t="n">
+        <v>2</v>
+      </c>
+      <c r="J521" t="n">
+        <v>1</v>
+      </c>
+      <c r="K521" t="n">
+        <v>1</v>
+      </c>
+      <c r="L521" t="n">
+        <v>2</v>
+      </c>
+      <c r="M521" t="n">
+        <v>0</v>
+      </c>
+      <c r="N521" t="n">
+        <v>1</v>
+      </c>
+      <c r="O521" t="n">
+        <v>0</v>
+      </c>
+      <c r="P521" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Adriano A</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Jimenez Winder</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>16</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>1</v>
+      </c>
+      <c r="H522" t="n">
+        <v>1</v>
+      </c>
+      <c r="I522" t="n">
+        <v>1</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="n">
+        <v>1</v>
+      </c>
+      <c r="L522" t="n">
+        <v>1</v>
+      </c>
+      <c r="M522" t="n">
+        <v>1</v>
+      </c>
+      <c r="N522" t="n">
+        <v>1</v>
+      </c>
+      <c r="O522" t="n">
+        <v>1</v>
+      </c>
+      <c r="P522" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Mathias A</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cardenas </t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>16</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="n">
+        <v>0</v>
+      </c>
+      <c r="M523" t="n">
+        <v>3</v>
+      </c>
+      <c r="N523" t="n">
+        <v>3</v>
+      </c>
+      <c r="O523" t="n">
+        <v>3</v>
+      </c>
+      <c r="P523" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Gabriel Kaled</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Conde Llontop</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>16</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>1</v>
+      </c>
+      <c r="H524" t="n">
+        <v>1</v>
+      </c>
+      <c r="I524" t="n">
+        <v>3</v>
+      </c>
+      <c r="J524" t="n">
+        <v>1</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" t="n">
+        <v>2</v>
+      </c>
+      <c r="M524" t="n">
+        <v>1</v>
+      </c>
+      <c r="N524" t="n">
+        <v>2</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Arleen Camila</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Zelaya Aramburú</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>16</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>2</v>
+      </c>
+      <c r="H525" t="n">
+        <v>2</v>
+      </c>
+      <c r="I525" t="n">
+        <v>3</v>
+      </c>
+      <c r="J525" t="n">
+        <v>2</v>
+      </c>
+      <c r="K525" t="n">
+        <v>3</v>
+      </c>
+      <c r="L525" t="n">
+        <v>3</v>
+      </c>
+      <c r="M525" t="n">
+        <v>2</v>
+      </c>
+      <c r="N525" t="n">
+        <v>1</v>
+      </c>
+      <c r="O525" t="n">
+        <v>2</v>
+      </c>
+      <c r="P525" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Nicole Stayce</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Gibson Garcia</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>16</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>1</v>
+      </c>
+      <c r="H526" t="n">
+        <v>1</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" t="n">
+        <v>1</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Gladys Rocio</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Cermeño</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>4to Secundaria</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>16</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>3</v>
+      </c>
+      <c r="H527" t="n">
+        <v>2</v>
+      </c>
+      <c r="I527" t="n">
+        <v>2</v>
+      </c>
+      <c r="J527" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" t="n">
+        <v>2</v>
+      </c>
+      <c r="L527" t="n">
+        <v>1</v>
+      </c>
+      <c r="M527" t="n">
+        <v>1</v>
+      </c>
+      <c r="N527" t="n">
+        <v>1</v>
+      </c>
+      <c r="O527" t="n">
+        <v>2</v>
+      </c>
+      <c r="P527" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>danna janice</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>velasquez</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>16</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>2</v>
+      </c>
+      <c r="H528" t="n">
+        <v>2</v>
+      </c>
+      <c r="I528" t="n">
+        <v>3</v>
+      </c>
+      <c r="J528" t="n">
+        <v>3</v>
+      </c>
+      <c r="K528" t="n">
+        <v>1</v>
+      </c>
+      <c r="L528" t="n">
+        <v>2</v>
+      </c>
+      <c r="M528" t="n">
+        <v>1</v>
+      </c>
+      <c r="N528" t="n">
+        <v>1</v>
+      </c>
+      <c r="O528" t="n">
+        <v>0</v>
+      </c>
+      <c r="P528" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Anna Mia</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Pesantes Meza</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>15</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>2</v>
+      </c>
+      <c r="H529" t="n">
+        <v>2</v>
+      </c>
+      <c r="I529" t="n">
+        <v>2</v>
+      </c>
+      <c r="J529" t="n">
+        <v>1</v>
+      </c>
+      <c r="K529" t="n">
+        <v>3</v>
+      </c>
+      <c r="L529" t="n">
+        <v>3</v>
+      </c>
+      <c r="M529" t="n">
+        <v>1</v>
+      </c>
+      <c r="N529" t="n">
+        <v>3</v>
+      </c>
+      <c r="O529" t="n">
+        <v>1</v>
+      </c>
+      <c r="P529" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Julietta Mia</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mogollón Menéndez </t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>16</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>2</v>
+      </c>
+      <c r="H530" t="n">
+        <v>2</v>
+      </c>
+      <c r="I530" t="n">
+        <v>3</v>
+      </c>
+      <c r="J530" t="n">
+        <v>2</v>
+      </c>
+      <c r="K530" t="n">
+        <v>3</v>
+      </c>
+      <c r="L530" t="n">
+        <v>2</v>
+      </c>
+      <c r="M530" t="n">
+        <v>1</v>
+      </c>
+      <c r="N530" t="n">
+        <v>1</v>
+      </c>
+      <c r="O530" t="n">
+        <v>2</v>
+      </c>
+      <c r="P530" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Estrella Fiorella</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Curasma Ramirez</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>15</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>2</v>
+      </c>
+      <c r="H531" t="n">
+        <v>2</v>
+      </c>
+      <c r="I531" t="n">
+        <v>1</v>
+      </c>
+      <c r="J531" t="n">
+        <v>1</v>
+      </c>
+      <c r="K531" t="n">
+        <v>1</v>
+      </c>
+      <c r="L531" t="n">
+        <v>1</v>
+      </c>
+      <c r="M531" t="n">
+        <v>1</v>
+      </c>
+      <c r="N531" t="n">
+        <v>1</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Yilmer Esteban</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Centti</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>16</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>1</v>
+      </c>
+      <c r="H532" t="n">
+        <v>3</v>
+      </c>
+      <c r="I532" t="n">
+        <v>3</v>
+      </c>
+      <c r="J532" t="n">
+        <v>3</v>
+      </c>
+      <c r="K532" t="n">
+        <v>0</v>
+      </c>
+      <c r="L532" t="n">
+        <v>0</v>
+      </c>
+      <c r="M532" t="n">
+        <v>3</v>
+      </c>
+      <c r="N532" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" t="n">
+        <v>3</v>
+      </c>
+      <c r="P532" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Adrian Kazuo</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>16</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>3</v>
+      </c>
+      <c r="H533" t="n">
+        <v>3</v>
+      </c>
+      <c r="I533" t="n">
+        <v>3</v>
+      </c>
+      <c r="J533" t="n">
+        <v>3</v>
+      </c>
+      <c r="K533" t="n">
+        <v>3</v>
+      </c>
+      <c r="L533" t="n">
+        <v>3</v>
+      </c>
+      <c r="M533" t="n">
+        <v>3</v>
+      </c>
+      <c r="N533" t="n">
+        <v>3</v>
+      </c>
+      <c r="O533" t="n">
+        <v>3</v>
+      </c>
+      <c r="P533" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Treizy Xiomara</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Gutierrez</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>16</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>3</v>
+      </c>
+      <c r="H534" t="n">
+        <v>1</v>
+      </c>
+      <c r="I534" t="n">
+        <v>1</v>
+      </c>
+      <c r="J534" t="n">
+        <v>2</v>
+      </c>
+      <c r="K534" t="n">
+        <v>1</v>
+      </c>
+      <c r="L534" t="n">
+        <v>3</v>
+      </c>
+      <c r="M534" t="n">
+        <v>1</v>
+      </c>
+      <c r="N534" t="n">
+        <v>1</v>
+      </c>
+      <c r="O534" t="n">
+        <v>3</v>
+      </c>
+      <c r="P534" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Erick Santiago</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Vasquez Valverde</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>16</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G535" t="n">
+        <v>1</v>
+      </c>
+      <c r="H535" t="n">
+        <v>1</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" t="n">
+        <v>2</v>
+      </c>
+      <c r="K535" t="n">
+        <v>1</v>
+      </c>
+      <c r="L535" t="n">
+        <v>0</v>
+      </c>
+      <c r="M535" t="n">
+        <v>2</v>
+      </c>
+      <c r="N535" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>0</v>
+      </c>
+      <c r="P535" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Thiago</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Castillo Diaz</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>16</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G536" t="n">
+        <v>1</v>
+      </c>
+      <c r="H536" t="n">
+        <v>1</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0</v>
+      </c>
+      <c r="K536" t="n">
+        <v>1</v>
+      </c>
+      <c r="L536" t="n">
+        <v>1</v>
+      </c>
+      <c r="M536" t="n">
+        <v>2</v>
+      </c>
+      <c r="N536" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" t="n">
+        <v>0</v>
+      </c>
+      <c r="P536" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Sebastian A</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Olin Vilca</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>16</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G537" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
+        <v>2</v>
+      </c>
+      <c r="J537" t="n">
+        <v>1</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" t="n">
+        <v>0</v>
+      </c>
+      <c r="N537" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>0</v>
+      </c>
+      <c r="P537" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>José a</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>16</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>1</v>
+      </c>
+      <c r="H538" t="n">
+        <v>1</v>
+      </c>
+      <c r="I538" t="n">
+        <v>1</v>
+      </c>
+      <c r="J538" t="n">
+        <v>1</v>
+      </c>
+      <c r="K538" t="n">
+        <v>1</v>
+      </c>
+      <c r="L538" t="n">
+        <v>1</v>
+      </c>
+      <c r="M538" t="n">
+        <v>1</v>
+      </c>
+      <c r="N538" t="n">
+        <v>1</v>
+      </c>
+      <c r="O538" t="n">
+        <v>1</v>
+      </c>
+      <c r="P538" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grigori Arturo </t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>rasputin</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>4to Sec</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>15</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H539" t="n">
+        <v>1</v>
+      </c>
+      <c r="I539" t="n">
+        <v>1</v>
+      </c>
+      <c r="J539" t="n">
+        <v>1</v>
+      </c>
+      <c r="K539" t="n">
+        <v>1</v>
+      </c>
+      <c r="L539" t="n">
+        <v>0</v>
+      </c>
+      <c r="M539" t="n">
+        <v>1</v>
+      </c>
+      <c r="N539" t="n">
+        <v>0</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0</v>
+      </c>
+      <c r="P539" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Angel Gabriel</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Quiroz Rivas</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>4to secundaria</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>15</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>0</v>
+      </c>
+      <c r="H540" t="n">
+        <v>1</v>
+      </c>
+      <c r="I540" t="n">
+        <v>3</v>
+      </c>
+      <c r="J540" t="n">
+        <v>0</v>
+      </c>
+      <c r="K540" t="n">
+        <v>1</v>
+      </c>
+      <c r="L540" t="n">
+        <v>0</v>
+      </c>
+      <c r="M540" t="n">
+        <v>3</v>
+      </c>
+      <c r="N540" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" t="n">
+        <v>0</v>
+      </c>
+      <c r="P540" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Brian M</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Cuya Pelaez</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>16</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G541" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>0</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" t="n">
+        <v>0</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0</v>
+      </c>
+      <c r="N541" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>1</v>
+      </c>
+      <c r="P541" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Patrick Gueiner</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Villalobos</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>16</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G542" t="n">
+        <v>0</v>
+      </c>
+      <c r="H542" t="n">
+        <v>1</v>
+      </c>
+      <c r="I542" t="n">
+        <v>1</v>
+      </c>
+      <c r="J542" t="n">
+        <v>1</v>
+      </c>
+      <c r="K542" t="n">
+        <v>0</v>
+      </c>
+      <c r="L542" t="n">
+        <v>0</v>
+      </c>
+      <c r="M542" t="n">
+        <v>1</v>
+      </c>
+      <c r="N542" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0</v>
+      </c>
+      <c r="P542" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Leandro Guillermo</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>MIlla Hernández</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>16</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G543" t="n">
+        <v>1</v>
+      </c>
+      <c r="H543" t="n">
+        <v>1</v>
+      </c>
+      <c r="I543" t="n">
+        <v>1</v>
+      </c>
+      <c r="J543" t="n">
+        <v>1</v>
+      </c>
+      <c r="K543" t="n">
+        <v>1</v>
+      </c>
+      <c r="L543" t="n">
+        <v>1</v>
+      </c>
+      <c r="M543" t="n">
+        <v>1</v>
+      </c>
+      <c r="N543" t="n">
+        <v>1</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Rodrigo A</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>16</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G544" t="n">
+        <v>1</v>
+      </c>
+      <c r="H544" t="n">
+        <v>1</v>
+      </c>
+      <c r="I544" t="n">
+        <v>1</v>
+      </c>
+      <c r="J544" t="n">
+        <v>1</v>
+      </c>
+      <c r="K544" t="n">
+        <v>2</v>
+      </c>
+      <c r="L544" t="n">
+        <v>0</v>
+      </c>
+      <c r="M544" t="n">
+        <v>2</v>
+      </c>
+      <c r="N544" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" t="n">
+        <v>3</v>
+      </c>
+      <c r="P544" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>15</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G545" t="n">
+        <v>1</v>
+      </c>
+      <c r="H545" t="n">
+        <v>1</v>
+      </c>
+      <c r="I545" t="n">
+        <v>3</v>
+      </c>
+      <c r="J545" t="n">
+        <v>2</v>
+      </c>
+      <c r="K545" t="n">
+        <v>1</v>
+      </c>
+      <c r="L545" t="n">
+        <v>1</v>
+      </c>
+      <c r="M545" t="n">
+        <v>3</v>
+      </c>
+      <c r="N545" t="n">
+        <v>1</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0</v>
+      </c>
+      <c r="P545" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Airton Sebastian</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Velasquez</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>15</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G546" t="n">
+        <v>1</v>
+      </c>
+      <c r="H546" t="n">
+        <v>1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>1</v>
+      </c>
+      <c r="J546" t="n">
+        <v>0</v>
+      </c>
+      <c r="K546" t="n">
+        <v>0</v>
+      </c>
+      <c r="L546" t="n">
+        <v>0</v>
+      </c>
+      <c r="M546" t="n">
+        <v>1</v>
+      </c>
+      <c r="N546" t="n">
+        <v>0</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0</v>
+      </c>
+      <c r="P546" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Axel G</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Vasquez M</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>4to A</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>15</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G547" t="n">
+        <v>3</v>
+      </c>
+      <c r="H547" t="n">
+        <v>2</v>
+      </c>
+      <c r="I547" t="n">
+        <v>1</v>
+      </c>
+      <c r="J547" t="n">
+        <v>2</v>
+      </c>
+      <c r="K547" t="n">
+        <v>1</v>
+      </c>
+      <c r="L547" t="n">
+        <v>3</v>
+      </c>
+      <c r="M547" t="n">
+        <v>1</v>
+      </c>
+      <c r="N547" t="n">
+        <v>1</v>
+      </c>
+      <c r="O547" t="n">
+        <v>3</v>
+      </c>
+      <c r="P547" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Andrea N</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Dulanto</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>16</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G548" t="n">
+        <v>2</v>
+      </c>
+      <c r="H548" t="n">
+        <v>2</v>
+      </c>
+      <c r="I548" t="n">
+        <v>2</v>
+      </c>
+      <c r="J548" t="n">
+        <v>1</v>
+      </c>
+      <c r="K548" t="n">
+        <v>3</v>
+      </c>
+      <c r="L548" t="n">
+        <v>1</v>
+      </c>
+      <c r="M548" t="n">
+        <v>1</v>
+      </c>
+      <c r="N548" t="n">
+        <v>2</v>
+      </c>
+      <c r="O548" t="n">
+        <v>1</v>
+      </c>
+      <c r="P548" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Alex Fabricio</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Lector Soriano</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>15</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G549" t="n">
+        <v>1</v>
+      </c>
+      <c r="H549" t="n">
+        <v>2</v>
+      </c>
+      <c r="I549" t="n">
+        <v>1</v>
+      </c>
+      <c r="J549" t="n">
+        <v>2</v>
+      </c>
+      <c r="K549" t="n">
+        <v>2</v>
+      </c>
+      <c r="L549" t="n">
+        <v>0</v>
+      </c>
+      <c r="M549" t="n">
+        <v>1</v>
+      </c>
+      <c r="N549" t="n">
+        <v>3</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0</v>
+      </c>
+      <c r="P549" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Melany C</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Caballero</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>16</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G550" t="n">
+        <v>3</v>
+      </c>
+      <c r="H550" t="n">
+        <v>2</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" t="n">
+        <v>3</v>
+      </c>
+      <c r="K550" t="n">
+        <v>1</v>
+      </c>
+      <c r="L550" t="n">
+        <v>3</v>
+      </c>
+      <c r="M550" t="n">
+        <v>2</v>
+      </c>
+      <c r="N550" t="n">
+        <v>2</v>
+      </c>
+      <c r="O550" t="n">
+        <v>3</v>
+      </c>
+      <c r="P550" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Nahiara</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>15</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G551" t="n">
+        <v>3</v>
+      </c>
+      <c r="H551" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>3</v>
+      </c>
+      <c r="J551" t="n">
+        <v>3</v>
+      </c>
+      <c r="K551" t="n">
+        <v>3</v>
+      </c>
+      <c r="L551" t="n">
+        <v>3</v>
+      </c>
+      <c r="M551" t="n">
+        <v>3</v>
+      </c>
+      <c r="N551" t="n">
+        <v>1</v>
+      </c>
+      <c r="O551" t="n">
+        <v>1</v>
+      </c>
+      <c r="P551" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Dania B</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Tenorio</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>16</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G552" t="n">
+        <v>1</v>
+      </c>
+      <c r="H552" t="n">
+        <v>2</v>
+      </c>
+      <c r="I552" t="n">
+        <v>1</v>
+      </c>
+      <c r="J552" t="n">
+        <v>1</v>
+      </c>
+      <c r="K552" t="n">
+        <v>1</v>
+      </c>
+      <c r="L552" t="n">
+        <v>1</v>
+      </c>
+      <c r="M552" t="n">
+        <v>1</v>
+      </c>
+      <c r="N552" t="n">
+        <v>2</v>
+      </c>
+      <c r="O552" t="n">
+        <v>1</v>
+      </c>
+      <c r="P552" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Fatima J</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Garay</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>16</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G553" t="n">
+        <v>1</v>
+      </c>
+      <c r="H553" t="n">
+        <v>3</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" t="n">
+        <v>2</v>
+      </c>
+      <c r="K553" t="n">
+        <v>3</v>
+      </c>
+      <c r="L553" t="n">
+        <v>3</v>
+      </c>
+      <c r="M553" t="n">
+        <v>1</v>
+      </c>
+      <c r="N553" t="n">
+        <v>1</v>
+      </c>
+      <c r="O553" t="n">
+        <v>3</v>
+      </c>
+      <c r="P553" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>rey ivan</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>lurbes N</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>4 A</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>17</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G554" t="n">
+        <v>1</v>
+      </c>
+      <c r="H554" t="n">
+        <v>1</v>
+      </c>
+      <c r="I554" t="n">
+        <v>1</v>
+      </c>
+      <c r="J554" t="n">
+        <v>1</v>
+      </c>
+      <c r="K554" t="n">
+        <v>1</v>
+      </c>
+      <c r="L554" t="n">
+        <v>2</v>
+      </c>
+      <c r="M554" t="n">
+        <v>1</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>0</v>
+      </c>
+      <c r="P554" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Melany Christal</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Caballero</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>4to</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>16</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G555" t="n">
+        <v>3</v>
+      </c>
+      <c r="H555" t="n">
+        <v>2</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0</v>
+      </c>
+      <c r="J555" t="n">
+        <v>3</v>
+      </c>
+      <c r="K555" t="n">
+        <v>2</v>
+      </c>
+      <c r="L555" t="n">
+        <v>3</v>
+      </c>
+      <c r="M555" t="n">
+        <v>3</v>
+      </c>
+      <c r="N555" t="n">
+        <v>2</v>
+      </c>
+      <c r="O555" t="n">
+        <v>3</v>
+      </c>
+      <c r="P555" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Brigith J</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Castillo Vasquez</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>15</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" t="n">
+        <v>1</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="n">
+        <v>1</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0</v>
+      </c>
+      <c r="L556" t="n">
+        <v>0</v>
+      </c>
+      <c r="M556" t="n">
+        <v>1</v>
+      </c>
+      <c r="N556" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" t="n">
+        <v>0</v>
+      </c>
+      <c r="P556" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>luis</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Céspedes</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>14</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>0</v>
+      </c>
+      <c r="H557" t="n">
+        <v>1</v>
+      </c>
+      <c r="I557" t="n">
+        <v>1</v>
+      </c>
+      <c r="J557" t="n">
+        <v>1</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0</v>
+      </c>
+      <c r="L557" t="n">
+        <v>0</v>
+      </c>
+      <c r="M557" t="n">
+        <v>1</v>
+      </c>
+      <c r="N557" t="n">
+        <v>0</v>
+      </c>
+      <c r="O557" t="n">
+        <v>0</v>
+      </c>
+      <c r="P557" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>olenka</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>15</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>3</v>
+      </c>
+      <c r="H558" t="n">
+        <v>2</v>
+      </c>
+      <c r="I558" t="n">
+        <v>3</v>
+      </c>
+      <c r="J558" t="n">
+        <v>2</v>
+      </c>
+      <c r="K558" t="n">
+        <v>1</v>
+      </c>
+      <c r="L558" t="n">
+        <v>3</v>
+      </c>
+      <c r="M558" t="n">
+        <v>1</v>
+      </c>
+      <c r="N558" t="n">
+        <v>1</v>
+      </c>
+      <c r="O558" t="n">
+        <v>2</v>
+      </c>
+      <c r="P558" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathias </t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rios </t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>3B Secundaria</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>15</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>3</v>
+      </c>
+      <c r="H559" t="n">
+        <v>1</v>
+      </c>
+      <c r="I559" t="n">
+        <v>3</v>
+      </c>
+      <c r="J559" t="n">
+        <v>2</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" t="n">
+        <v>1</v>
+      </c>
+      <c r="M559" t="n">
+        <v>0</v>
+      </c>
+      <c r="N559" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" t="n">
+        <v>0</v>
+      </c>
+      <c r="P559" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>15</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>1</v>
+      </c>
+      <c r="H560" t="n">
+        <v>1</v>
+      </c>
+      <c r="I560" t="n">
+        <v>1</v>
+      </c>
+      <c r="J560" t="n">
+        <v>1</v>
+      </c>
+      <c r="K560" t="n">
+        <v>1</v>
+      </c>
+      <c r="L560" t="n">
+        <v>1</v>
+      </c>
+      <c r="M560" t="n">
+        <v>1</v>
+      </c>
+      <c r="N560" t="n">
+        <v>1</v>
+      </c>
+      <c r="O560" t="n">
+        <v>0</v>
+      </c>
+      <c r="P560" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>15</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>1</v>
+      </c>
+      <c r="H561" t="n">
+        <v>1</v>
+      </c>
+      <c r="I561" t="n">
+        <v>3</v>
+      </c>
+      <c r="J561" t="n">
+        <v>2</v>
+      </c>
+      <c r="K561" t="n">
+        <v>1</v>
+      </c>
+      <c r="L561" t="n">
+        <v>2</v>
+      </c>
+      <c r="M561" t="n">
+        <v>2</v>
+      </c>
+      <c r="N561" t="n">
+        <v>1</v>
+      </c>
+      <c r="O561" t="n">
+        <v>0</v>
+      </c>
+      <c r="P561" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Bruno Alejandro</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Gamarra Cisneros</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>3eroB</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>14</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>2</v>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>3</v>
+      </c>
+      <c r="J562" t="n">
+        <v>3</v>
+      </c>
+      <c r="K562" t="n">
+        <v>1</v>
+      </c>
+      <c r="L562" t="n">
+        <v>0</v>
+      </c>
+      <c r="M562" t="n">
+        <v>1</v>
+      </c>
+      <c r="N562" t="n">
+        <v>2</v>
+      </c>
+      <c r="O562" t="n">
+        <v>0</v>
+      </c>
+      <c r="P562" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ariana </t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Lescano</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>14</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G563" t="n">
+        <v>1</v>
+      </c>
+      <c r="H563" t="n">
+        <v>1</v>
+      </c>
+      <c r="I563" t="n">
+        <v>2</v>
+      </c>
+      <c r="J563" t="n">
+        <v>1</v>
+      </c>
+      <c r="K563" t="n">
+        <v>1</v>
+      </c>
+      <c r="L563" t="n">
+        <v>2</v>
+      </c>
+      <c r="M563" t="n">
+        <v>0</v>
+      </c>
+      <c r="N563" t="n">
+        <v>1</v>
+      </c>
+      <c r="O563" t="n">
+        <v>0</v>
+      </c>
+      <c r="P563" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Jheremy Saul</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Roca Medina</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>15</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>1</v>
+      </c>
+      <c r="H564" t="n">
+        <v>1</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" t="n">
+        <v>0</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" t="n">
+        <v>0</v>
+      </c>
+      <c r="M564" t="n">
+        <v>1</v>
+      </c>
+      <c r="N564" t="n">
+        <v>1</v>
+      </c>
+      <c r="O564" t="n">
+        <v>0</v>
+      </c>
+      <c r="P564" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>María Fernanda</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Gómez</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>15</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>2</v>
+      </c>
+      <c r="H565" t="n">
+        <v>2</v>
+      </c>
+      <c r="I565" t="n">
+        <v>3</v>
+      </c>
+      <c r="J565" t="n">
+        <v>1</v>
+      </c>
+      <c r="K565" t="n">
+        <v>2</v>
+      </c>
+      <c r="L565" t="n">
+        <v>3</v>
+      </c>
+      <c r="M565" t="n">
+        <v>1</v>
+      </c>
+      <c r="N565" t="n">
+        <v>3</v>
+      </c>
+      <c r="O565" t="n">
+        <v>1</v>
+      </c>
+      <c r="P565" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cesar andre </t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>velasquez lecarnaque</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>3roB secundaria</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>14</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>1</v>
+      </c>
+      <c r="H566" t="n">
+        <v>1</v>
+      </c>
+      <c r="I566" t="n">
+        <v>1</v>
+      </c>
+      <c r="J566" t="n">
+        <v>1</v>
+      </c>
+      <c r="K566" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" t="n">
+        <v>0</v>
+      </c>
+      <c r="N566" t="n">
+        <v>1</v>
+      </c>
+      <c r="O566" t="n">
+        <v>0</v>
+      </c>
+      <c r="P566" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Mathias Sebastian</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Piscoya Mateo</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>14</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G567" t="n">
+        <v>1</v>
+      </c>
+      <c r="H567" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0</v>
+      </c>
+      <c r="J567" t="n">
+        <v>1</v>
+      </c>
+      <c r="K567" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" t="n">
+        <v>0</v>
+      </c>
+      <c r="M567" t="n">
+        <v>0</v>
+      </c>
+      <c r="N567" t="n">
+        <v>1</v>
+      </c>
+      <c r="O567" t="n">
+        <v>0</v>
+      </c>
+      <c r="P567" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Naomi Rosy</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Palomino Marcelo</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>15</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G568" t="n">
+        <v>3</v>
+      </c>
+      <c r="H568" t="n">
+        <v>3</v>
+      </c>
+      <c r="I568" t="n">
+        <v>3</v>
+      </c>
+      <c r="J568" t="n">
+        <v>3</v>
+      </c>
+      <c r="K568" t="n">
+        <v>3</v>
+      </c>
+      <c r="L568" t="n">
+        <v>3</v>
+      </c>
+      <c r="M568" t="n">
+        <v>3</v>
+      </c>
+      <c r="N568" t="n">
+        <v>3</v>
+      </c>
+      <c r="O568" t="n">
+        <v>1</v>
+      </c>
+      <c r="P568" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Valentina Zoe</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Vásquez Prinque</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>3ero</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>14</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G569" t="n">
+        <v>3</v>
+      </c>
+      <c r="H569" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>1</v>
+      </c>
+      <c r="J569" t="n">
+        <v>2</v>
+      </c>
+      <c r="K569" t="n">
+        <v>2</v>
+      </c>
+      <c r="L569" t="n">
+        <v>1</v>
+      </c>
+      <c r="M569" t="n">
+        <v>2</v>
+      </c>
+      <c r="N569" t="n">
+        <v>1</v>
+      </c>
+      <c r="O569" t="n">
+        <v>0</v>
+      </c>
+      <c r="P569" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Angie N</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goicochea Cordova </t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>3ero</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>14</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G570" t="n">
+        <v>3</v>
+      </c>
+      <c r="H570" t="n">
+        <v>2</v>
+      </c>
+      <c r="I570" t="n">
+        <v>3</v>
+      </c>
+      <c r="J570" t="n">
+        <v>2</v>
+      </c>
+      <c r="K570" t="n">
+        <v>3</v>
+      </c>
+      <c r="L570" t="n">
+        <v>3</v>
+      </c>
+      <c r="M570" t="n">
+        <v>3</v>
+      </c>
+      <c r="N570" t="n">
+        <v>3</v>
+      </c>
+      <c r="O570" t="n">
+        <v>1</v>
+      </c>
+      <c r="P570" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Yazury V</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Cervantes Rivera</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>14</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G571" t="n">
+        <v>2</v>
+      </c>
+      <c r="H571" t="n">
+        <v>1</v>
+      </c>
+      <c r="I571" t="n">
+        <v>2</v>
+      </c>
+      <c r="J571" t="n">
+        <v>3</v>
+      </c>
+      <c r="K571" t="n">
+        <v>1</v>
+      </c>
+      <c r="L571" t="n">
+        <v>3</v>
+      </c>
+      <c r="M571" t="n">
+        <v>1</v>
+      </c>
+      <c r="N571" t="n">
+        <v>2</v>
+      </c>
+      <c r="O571" t="n">
+        <v>3</v>
+      </c>
+      <c r="P571" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>María J</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Alvarado Bocanegra</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>14</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G572" t="n">
+        <v>2</v>
+      </c>
+      <c r="H572" t="n">
+        <v>1</v>
+      </c>
+      <c r="I572" t="n">
+        <v>1</v>
+      </c>
+      <c r="J572" t="n">
+        <v>2</v>
+      </c>
+      <c r="K572" t="n">
+        <v>1</v>
+      </c>
+      <c r="L572" t="n">
+        <v>2</v>
+      </c>
+      <c r="M572" t="n">
+        <v>1</v>
+      </c>
+      <c r="N572" t="n">
+        <v>1</v>
+      </c>
+      <c r="O572" t="n">
+        <v>0</v>
+      </c>
+      <c r="P572" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Fernando Valentino</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daga </t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>14</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G573" t="n">
+        <v>0</v>
+      </c>
+      <c r="H573" t="n">
+        <v>1</v>
+      </c>
+      <c r="I573" t="n">
+        <v>1</v>
+      </c>
+      <c r="J573" t="n">
+        <v>1</v>
+      </c>
+      <c r="K573" t="n">
+        <v>1</v>
+      </c>
+      <c r="L573" t="n">
+        <v>1</v>
+      </c>
+      <c r="M573" t="n">
+        <v>1</v>
+      </c>
+      <c r="N573" t="n">
+        <v>0</v>
+      </c>
+      <c r="O573" t="n">
+        <v>0</v>
+      </c>
+      <c r="P573" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>José Á</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Seminario Cueva</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>15</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G574" t="n">
+        <v>0</v>
+      </c>
+      <c r="H574" t="n">
+        <v>1</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" t="n">
+        <v>1</v>
+      </c>
+      <c r="K574" t="n">
+        <v>0</v>
+      </c>
+      <c r="L574" t="n">
+        <v>0</v>
+      </c>
+      <c r="M574" t="n">
+        <v>0</v>
+      </c>
+      <c r="N574" t="n">
+        <v>0</v>
+      </c>
+      <c r="O574" t="n">
+        <v>0</v>
+      </c>
+      <c r="P574" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Valeria N</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Zamora Valverde</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>15</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G575" t="n">
+        <v>3</v>
+      </c>
+      <c r="H575" t="n">
+        <v>3</v>
+      </c>
+      <c r="I575" t="n">
+        <v>2</v>
+      </c>
+      <c r="J575" t="n">
+        <v>3</v>
+      </c>
+      <c r="K575" t="n">
+        <v>2</v>
+      </c>
+      <c r="L575" t="n">
+        <v>0</v>
+      </c>
+      <c r="M575" t="n">
+        <v>3</v>
+      </c>
+      <c r="N575" t="n">
+        <v>3</v>
+      </c>
+      <c r="O575" t="n">
+        <v>1</v>
+      </c>
+      <c r="P575" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Ricardo M</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>velazquez</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>3ero</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>15</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G576" t="n">
+        <v>1</v>
+      </c>
+      <c r="H576" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" t="n">
+        <v>1</v>
+      </c>
+      <c r="J576" t="n">
+        <v>2</v>
+      </c>
+      <c r="K576" t="n">
+        <v>1</v>
+      </c>
+      <c r="L576" t="n">
+        <v>1</v>
+      </c>
+      <c r="M576" t="n">
+        <v>1</v>
+      </c>
+      <c r="N576" t="n">
+        <v>2</v>
+      </c>
+      <c r="O576" t="n">
+        <v>0</v>
+      </c>
+      <c r="P576" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Hiro Renato</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Fukunaga Gonzales</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>3er Grado - Sec</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>15</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G577" t="n">
+        <v>1</v>
+      </c>
+      <c r="H577" t="n">
+        <v>1</v>
+      </c>
+      <c r="I577" t="n">
+        <v>1</v>
+      </c>
+      <c r="J577" t="n">
+        <v>1</v>
+      </c>
+      <c r="K577" t="n">
+        <v>1</v>
+      </c>
+      <c r="L577" t="n">
+        <v>0</v>
+      </c>
+      <c r="M577" t="n">
+        <v>0</v>
+      </c>
+      <c r="N577" t="n">
+        <v>1</v>
+      </c>
+      <c r="O577" t="n">
+        <v>0</v>
+      </c>
+      <c r="P577" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Leonardo A</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Velasquez Mendez</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>15</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G578" t="n">
+        <v>1</v>
+      </c>
+      <c r="H578" t="n">
+        <v>1</v>
+      </c>
+      <c r="I578" t="n">
+        <v>2</v>
+      </c>
+      <c r="J578" t="n">
+        <v>1</v>
+      </c>
+      <c r="K578" t="n">
+        <v>0</v>
+      </c>
+      <c r="L578" t="n">
+        <v>0</v>
+      </c>
+      <c r="M578" t="n">
+        <v>1</v>
+      </c>
+      <c r="N578" t="n">
+        <v>0</v>
+      </c>
+      <c r="O578" t="n">
+        <v>0</v>
+      </c>
+      <c r="P578" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>giancarlo a</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">calderon </t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>3ero</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>14</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G579" t="n">
+        <v>1</v>
+      </c>
+      <c r="H579" t="n">
+        <v>0</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="n">
+        <v>1</v>
+      </c>
+      <c r="K579" t="n">
+        <v>0</v>
+      </c>
+      <c r="L579" t="n">
+        <v>0</v>
+      </c>
+      <c r="M579" t="n">
+        <v>1</v>
+      </c>
+      <c r="N579" t="n">
+        <v>1</v>
+      </c>
+      <c r="O579" t="n">
+        <v>0</v>
+      </c>
+      <c r="P579" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Alexia Nayira</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>15</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G580" t="n">
+        <v>1</v>
+      </c>
+      <c r="H580" t="n">
+        <v>1</v>
+      </c>
+      <c r="I580" t="n">
+        <v>1</v>
+      </c>
+      <c r="J580" t="n">
+        <v>1</v>
+      </c>
+      <c r="K580" t="n">
+        <v>1</v>
+      </c>
+      <c r="L580" t="n">
+        <v>1</v>
+      </c>
+      <c r="M580" t="n">
+        <v>1</v>
+      </c>
+      <c r="N580" t="n">
+        <v>0</v>
+      </c>
+      <c r="O580" t="n">
+        <v>1</v>
+      </c>
+      <c r="P580" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>liam a</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>zorrilla</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>3 b</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>16</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G581" t="n">
+        <v>1</v>
+      </c>
+      <c r="H581" t="n">
+        <v>2</v>
+      </c>
+      <c r="I581" t="n">
+        <v>3</v>
+      </c>
+      <c r="J581" t="n">
+        <v>1</v>
+      </c>
+      <c r="K581" t="n">
+        <v>0</v>
+      </c>
+      <c r="L581" t="n">
+        <v>0</v>
+      </c>
+      <c r="M581" t="n">
+        <v>0</v>
+      </c>
+      <c r="N581" t="n">
+        <v>3</v>
+      </c>
+      <c r="O581" t="n">
+        <v>0</v>
+      </c>
+      <c r="P581" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Gabriela G</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Ccuno C</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>3ero B</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>15</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G582" t="n">
+        <v>1</v>
+      </c>
+      <c r="H582" t="n">
+        <v>3</v>
+      </c>
+      <c r="I582" t="n">
+        <v>3</v>
+      </c>
+      <c r="J582" t="n">
+        <v>1</v>
+      </c>
+      <c r="K582" t="n">
+        <v>1</v>
+      </c>
+      <c r="L582" t="n">
+        <v>3</v>
+      </c>
+      <c r="M582" t="n">
+        <v>3</v>
+      </c>
+      <c r="N582" t="n">
+        <v>2</v>
+      </c>
+      <c r="O582" t="n">
+        <v>0</v>
+      </c>
+      <c r="P582" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>Moderadamente grave</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Xiomara R</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Bernuy Gil</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>3ro</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>15</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>estudiante</t>
+        </is>
+      </c>
+      <c r="G583" t="n">
+        <v>2</v>
+      </c>
+      <c r="H583" t="n">
+        <v>2</v>
+      </c>
+      <c r="I583" t="n">
+        <v>1</v>
+      </c>
+      <c r="J583" t="n">
+        <v>2</v>
+      </c>
+      <c r="K583" t="n">
+        <v>1</v>
+      </c>
+      <c r="L583" t="n">
+        <v>0</v>
+      </c>
+      <c r="M583" t="n">
+        <v>1</v>
+      </c>
+      <c r="N583" t="n">
+        <v>1</v>
+      </c>
+      <c r="O583" t="n">
+        <v>1</v>
+      </c>
+      <c r="P583" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
